--- a/ig/main/alignement-nuva-bdpm.xlsx
+++ b/ig/main/alignement-nuva-bdpm.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.818</t>
+    <t>1.0.825</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-05</t>
+    <t>2025-01-06</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -564,6 +564,18 @@
     <t>COMIRNATY OMICRON XBB.1.5 30 microgrammes/dose, dispersion injectable. Vaccin à ARNm (à nucléoside modifié) contre la COVID-19</t>
   </si>
   <si>
+    <t>VAC0620</t>
+  </si>
+  <si>
+    <t>IXCHIQ</t>
+  </si>
+  <si>
+    <t>3400930296448</t>
+  </si>
+  <si>
+    <t>IXCHIQ, poudre et solvant pour solution injectable. Vaccin contre le chikungunya (vivant) 1 flacon unidose en verre + 1 seringue préremplie en verre de 0,5 mL</t>
+  </si>
+  <si>
     <t>VAC0050</t>
   </si>
   <si>
@@ -1194,18 +1206,6 @@
     <t>SHINGRIX, poudre et suspension pour suspension injectable. Vaccin zona (recombinant, avec adjuvant) 1 flacon en verre de 50 microgrammes de poudre  - 1 flacon en verre de 0,5 ml de suspension</t>
   </si>
   <si>
-    <t>VAC0010</t>
-  </si>
-  <si>
-    <t>HBVAXPRO 40 µg</t>
-  </si>
-  <si>
-    <t>64757607</t>
-  </si>
-  <si>
-    <t>HBVAXPRO 40 microgrammes, suspension injectable. Vaccin de l'hépatite B (ADNr)</t>
-  </si>
-  <si>
     <t>VAC0562</t>
   </si>
   <si>
@@ -1755,13 +1755,13 @@
     <t>65802140</t>
   </si>
   <si>
-    <t>TRUMENBA, suspension injectable en seringue préremplie</t>
+    <t>TRUMENBA, suspension injectable en seringue préremplie. Vaccin méningococcique groupe B (recombinant, adsorbé)</t>
   </si>
   <si>
     <t>3400930096376</t>
   </si>
   <si>
-    <t>TRUMENBA, suspension injectable en seringue préremplie 1 seringue préremplie en verre de 0,5 ml avec aiguille</t>
+    <t>TRUMENBA, suspension injectable en seringue préremplie. Vaccin méningococcique groupe B (recombinant, adsorbé) 1 seringue préremplie en verre de 0,5 ml avec aiguille</t>
   </si>
 </sst>
 </file>
@@ -2963,27 +2963,27 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C56" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E56" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C57" t="s" s="2">
         <v>34</v>
@@ -2997,27 +2997,27 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C58" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C59" t="s" s="2">
         <v>34</v>
@@ -3031,27 +3031,27 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C60" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E60" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C61" t="s" s="2">
         <v>34</v>
@@ -3065,27 +3065,27 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C62" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C63" t="s" s="2">
         <v>34</v>
@@ -3116,61 +3116,61 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C65" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C66" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E66" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C67" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C68" t="s" s="2">
         <v>34</v>
@@ -3184,27 +3184,27 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C69" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D69" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E69" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C70" t="s" s="2">
         <v>34</v>
@@ -3218,27 +3218,27 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C71" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E71" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C72" t="s" s="2">
         <v>34</v>
@@ -3252,44 +3252,44 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C73" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C74" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E74" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C75" t="s" s="2">
         <v>34</v>
@@ -3303,61 +3303,61 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C76" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E76" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C77" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E77" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C78" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E78" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C79" t="s" s="2">
         <v>34</v>
@@ -3388,27 +3388,27 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C81" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C82" t="s" s="2">
         <v>34</v>
@@ -3422,27 +3422,27 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C83" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D83" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E83" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C84" t="s" s="2">
         <v>34</v>
@@ -3456,27 +3456,27 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C85" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E85" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C86" t="s" s="2">
         <v>34</v>
@@ -3490,44 +3490,44 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C87" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E87" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C88" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D88" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E88" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C89" t="s" s="2">
         <v>34</v>
@@ -3541,27 +3541,27 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C90" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D90" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E90" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C91" t="s" s="2">
         <v>34</v>
@@ -3575,27 +3575,27 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C92" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D92" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E92" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C93" t="s" s="2">
         <v>34</v>
@@ -3609,27 +3609,27 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C94" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D94" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E94" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C95" t="s" s="2">
         <v>34</v>
@@ -3643,27 +3643,27 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C96" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D96" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E96" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C97" t="s" s="2">
         <v>34</v>
@@ -3677,27 +3677,27 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C98" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D98" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E98" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C99" t="s" s="2">
         <v>34</v>
@@ -3711,27 +3711,27 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C100" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D100" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E100" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C101" t="s" s="2">
         <v>34</v>
@@ -3745,27 +3745,27 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C102" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D102" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E102" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C103" t="s" s="2">
         <v>34</v>
@@ -3779,27 +3779,27 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C104" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D104" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E104" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C105" t="s" s="2">
         <v>34</v>
@@ -3813,44 +3813,44 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C106" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D106" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E106" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C107" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D107" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E107" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C108" t="s" s="2">
         <v>34</v>
@@ -3864,27 +3864,27 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C109" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D109" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E109" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C110" t="s" s="2">
         <v>34</v>
@@ -3898,44 +3898,44 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C111" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D111" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E111" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C112" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D112" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E112" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C113" t="s" s="2">
         <v>34</v>
@@ -3949,27 +3949,27 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C114" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D114" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E114" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C115" t="s" s="2">
         <v>34</v>
@@ -3983,27 +3983,27 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C116" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D116" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E116" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C117" t="s" s="2">
         <v>34</v>
@@ -4017,27 +4017,27 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C118" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D118" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E118" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C119" t="s" s="2">
         <v>34</v>
@@ -4051,27 +4051,27 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C120" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D120" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E120" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C121" t="s" s="2">
         <v>34</v>
@@ -4085,27 +4085,27 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C122" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D122" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E122" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C123" t="s" s="2">
         <v>34</v>
@@ -4119,27 +4119,27 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C124" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D124" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E124" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C125" t="s" s="2">
         <v>34</v>
@@ -4153,27 +4153,27 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C126" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D126" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E126" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C127" t="s" s="2">
         <v>34</v>

--- a/ig/main/alignement-nuva-bdpm.xlsx
+++ b/ig/main/alignement-nuva-bdpm.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="577">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.825</t>
+    <t>1.0.854</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06</t>
+    <t>2025-02-11</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -156,36 +156,36 @@
     <t>COMIRNATY 3 µg 6 MOIS-4 ANS BIONTECH-PFIZER</t>
   </si>
   <si>
+    <t>3400930264058</t>
+  </si>
+  <si>
+    <t>COMIRNATY 3 microgrammes/dose, dispersion à diluer pour dispersion injectable.Vaccin à ARNm (à nucléoside modifié) contre la COVID-19 10 flacon(s) multidose(s) en verre de 10 dose(s) ( abrogée le 12/12/2024)</t>
+  </si>
+  <si>
     <t>63786926</t>
   </si>
   <si>
     <t>COMIRNATY 3 microgrammes/dose, dispersion à diluer pour dispersion injectable.Vaccin à ARNm (à nucléoside modifié) contre la COVID-19</t>
   </si>
   <si>
-    <t>3400930264058</t>
-  </si>
-  <si>
-    <t>COMIRNATY 3 microgrammes/dose, dispersion à diluer pour dispersion injectable.Vaccin à ARNm (à nucléoside modifié) contre la COVID-19 10 flacon(s) multidose(s) en verre de 10 dose(s)</t>
-  </si>
-  <si>
     <t>VAC0666</t>
   </si>
   <si>
     <t>JCOVDEN - COVID-19 VACCINE JANSSEN</t>
   </si>
   <si>
+    <t>3400930222232</t>
+  </si>
+  <si>
+    <t>JCOVDEN, suspension injectable Vaccin contre la COVID-19 (Ad26.COV2-S [recombinant]) 10 flacons multidoses en verre  de 5 doses</t>
+  </si>
+  <si>
     <t>64798803</t>
   </si>
   <si>
     <t>JCOVDEN, suspension injectable Vaccin contre la COVID-19 (Ad26.COV2-S recombinant)</t>
   </si>
   <si>
-    <t>3400930222232</t>
-  </si>
-  <si>
-    <t>JCOVDEN, suspension injectable Vaccin contre la COVID-19 (Ad26.COV2-S [recombinant]) 10 flacons multidoses en verre  de 5 doses</t>
-  </si>
-  <si>
     <t>3400930227015</t>
   </si>
   <si>
@@ -198,18 +198,18 @@
     <t>VACCIN RABIQUE PASTEUR</t>
   </si>
   <si>
+    <t>3400933048877</t>
+  </si>
+  <si>
+    <t>VACCIN RABIQUE PASTEUR, poudre et solvant pour suspension injectable. Vaccin rabique, inactivé 1 flacon(s) en verre - 1 seringue(s) préremplie(s) en verre de 0,5 ml avec aiguille(s) avec protège-aiguille</t>
+  </si>
+  <si>
     <t>67718545</t>
   </si>
   <si>
     <t>VACCIN RABIQUE PASTEUR, poudre et solvant pour suspension injectable. Vaccin rabique, inactivé</t>
   </si>
   <si>
-    <t>3400933048877</t>
-  </si>
-  <si>
-    <t>VACCIN RABIQUE PASTEUR, poudre et solvant pour suspension injectable. Vaccin rabique, inactivé 1 flacon(s) en verre - 1 seringue(s) préremplie(s) en verre de 0,5 ml avec aiguille(s) avec protège-aiguille</t>
-  </si>
-  <si>
     <t>VAC0017</t>
   </si>
   <si>
@@ -249,13 +249,13 @@
     <t>3400935167095</t>
   </si>
   <si>
-    <t>ENGERIX B 10 microgrammes/0,5 ml, suspension injectable en seringue préremplie. Vaccin de l'hépatite B (ADNr), (adsorbé) (VHB) 1 seringue(s) préremplie(s) en verre de 0,5 ml avec aiguille(s)</t>
+    <t>ENGERIX B 10 microgrammes/0,5 mL, suspension injectable en seringue préremplie. Vaccin de l'hépatite B (ADNr), (adsorbé) (VHB) 1 seringue(s) préremplie(s) en verre de 0,5 ml avec aiguille(s)</t>
   </si>
   <si>
     <t>65782652</t>
   </si>
   <si>
-    <t>ENGERIX B 10 microgrammes/0,5 ml, suspension injectable en seringue préremplie. Vaccin de l'hépatite B (ADNr), (adsorbé) (VHB)</t>
+    <t>ENGERIX B 10 microgrammes/0,5 mL, suspension injectable en seringue préremplie. Vaccin de l'hépatite B (ADNr), (adsorbé) (VHB)</t>
   </si>
   <si>
     <t>VAC0040</t>
@@ -264,18 +264,18 @@
     <t>TYAVAX</t>
   </si>
   <si>
+    <t>69725264</t>
+  </si>
+  <si>
+    <t>TYAVAX, suspension et solution pour suspension injectable en seringue préremplie. Vaccin de l'hépatite A (inactivé, adsorbé) et typhoïdique polyosidique</t>
+  </si>
+  <si>
     <t>3400936077836</t>
   </si>
   <si>
     <t>TYAVAX, suspension et solution pour suspension injectable en seringue préremplie. Vaccin de l'hépatite A (inactivé, adsorbé) et typhoïdique polyosidique 1 seringue(s) préremplie(s) bicompartimenté(e)(s)/à 2 compartiments en verre de 0,5 ml avec aiguille(s)</t>
   </si>
   <si>
-    <t>69725264</t>
-  </si>
-  <si>
-    <t>TYAVAX, suspension et solution pour suspension injectable en seringue préremplie. Vaccin de l'hépatite A (inactivé, adsorbé) et typhoïdique polyosidique</t>
-  </si>
-  <si>
     <t>VAC0003</t>
   </si>
   <si>
@@ -300,18 +300,18 @@
     <t>VIDPREVTYN BETA</t>
   </si>
   <si>
+    <t>3400930264157</t>
+  </si>
+  <si>
+    <t>VIDPREVTYN BETA, solution et émulsion pour émulsion injectable. Vaccin contre la COVID-19 (recombinant avec adjuvant) 10 flacon(s) multidose(s) de 10 doses  en verre de 2,5 mL- 10 flacon(s) multidose(s) de 10 doses en verre de 2,5 mL (100 doses),</t>
+  </si>
+  <si>
     <t>67734275</t>
   </si>
   <si>
     <t>VIDPREVTYN BETA, solution et émulsion pour émulsion injectable. Vaccin contre la COVID-19 (recombinant avec adjuvant)</t>
   </si>
   <si>
-    <t>3400930264157</t>
-  </si>
-  <si>
-    <t>VIDPREVTYN BETA, solution et émulsion pour émulsion injectable. Vaccin contre la COVID-19 (recombinant avec adjuvant) 10 flacon(s) multidose(s) de 10 doses  en verre de 2,5 mL- 10 flacon(s) multidose(s) de 10 doses en verre de 2,5 mL (100 doses),</t>
-  </si>
-  <si>
     <t>VAC0495</t>
   </si>
   <si>
@@ -345,7 +345,7 @@
     <t>3400930243404</t>
   </si>
   <si>
-    <t>COMIRNATY 10 microgrammes/dose, dispersion à diluer pour dispersion injectable.Vaccin à ARNm (à nucléoside modifié) contre la COVID-19 10 flacon(s) multidose(s) en verre de 10 dose(s)</t>
+    <t>COMIRNATY 10 microgrammes/dose, dispersion à diluer pour dispersion injectable.Vaccin à ARNm (à nucléoside modifié) contre la COVID-19 10 flacon(s) multidose(s) en verre de 10 dose(s) ( abrogée le 12/12/2024)</t>
   </si>
   <si>
     <t>VAC0073</t>
@@ -354,18 +354,18 @@
     <t>IXIARO</t>
   </si>
   <si>
+    <t>62816512</t>
+  </si>
+  <si>
+    <t>IXIARO, suspension injectable. Vaccin de l'encéphalite japonaise (inactivé, adsorbé)</t>
+  </si>
+  <si>
     <t>3400939395975</t>
   </si>
   <si>
     <t>IXIARO, suspension injectable. Vaccin de l'encéphalite japonaise (inactivé, adsorbé) 1 seringue(s) préremplie(s) en verre de 0,5 ml</t>
   </si>
   <si>
-    <t>62816512</t>
-  </si>
-  <si>
-    <t>IXIARO, suspension injectable. Vaccin de l'encéphalite japonaise (inactivé, adsorbé)</t>
-  </si>
-  <si>
     <t>VAC0031</t>
   </si>
   <si>
@@ -444,16 +444,16 @@
     <t>COMIRNATY ORIGINAL/OMICRON BA.4-5 (15/15 µg) BIONTECH-PFIZER</t>
   </si>
   <si>
+    <t>65590890</t>
+  </si>
+  <si>
+    <t>COMIRNATY ORIGINAL/OMICRON BA.4-5 (15/15 microgrammes)/dose, dispersion injectable. Vaccin à ARNm (à nucléoside modifié) contre la COVID-19</t>
+  </si>
+  <si>
     <t>3400930262009</t>
   </si>
   <si>
-    <t>COMIRNATY ORIGINAL/OMICRON BA.4-5 (15/15 microgrammes)/dose, dispersion injectable. Vaccin à ARNm (à nucléoside modifié) contre la COVID-19 10 flacon(s) multidose(s) en verre de 6 dose(s)</t>
-  </si>
-  <si>
-    <t>65590890</t>
-  </si>
-  <si>
-    <t>COMIRNATY ORIGINAL/OMICRON BA.4-5 (15/15 microgrammes)/dose, dispersion injectable. Vaccin à ARNm (à nucléoside modifié) contre la COVID-19</t>
+    <t>COMIRNATY ORIGINAL/OMICRON BA.4-5 (15/15 microgrammes)/dose, dispersion injectable. Vaccin à ARNm (à nucléoside modifié) contre la COVID-19 10 flacon(s) multidose(s) en verre de 6 dose(s) ( abrogée le 12/12/2024)</t>
   </si>
   <si>
     <t>VAC0579</t>
@@ -498,18 +498,18 @@
     <t>NEISVAC</t>
   </si>
   <si>
+    <t>3400936277397</t>
+  </si>
+  <si>
+    <t>NEISVAC, suspension injectable en seringue préremplie. Vaccin méningococcique polyosidique du groupe C (conjugué, adsorbé) 1 seringue(s) préremplie(s) en verre de 0,5 ml avec 2 aiguille(s)</t>
+  </si>
+  <si>
     <t>69261547</t>
   </si>
   <si>
     <t>NEISVAC, suspension injectable en seringue préremplie. Vaccin méningococcique polyosidique du groupe C (conjugué, adsorbé)</t>
   </si>
   <si>
-    <t>3400936277397</t>
-  </si>
-  <si>
-    <t>NEISVAC, suspension injectable en seringue préremplie. Vaccin méningococcique polyosidique du groupe C (conjugué, adsorbé) 1 seringue(s) préremplie(s) en verre de 0,5 ml avec 2 aiguille(s)</t>
-  </si>
-  <si>
     <t>VAC0115</t>
   </si>
   <si>
@@ -534,18 +534,18 @@
     <t>NUVAXOVID</t>
   </si>
   <si>
+    <t>69544189</t>
+  </si>
+  <si>
+    <t>NUVAXOVID, dispersion injectable. Vaccin contre la COVID-19 (recombinant avec adjuvant)</t>
+  </si>
+  <si>
     <t>3400930245774</t>
   </si>
   <si>
     <t>NUVAXOVID, dispersion injectable. Vaccin contre la COVID-19 (recombinant avec adjuvant) 10 flacons multidoses en verre de 5 mL de 10 doses (100 doses)</t>
   </si>
   <si>
-    <t>69544189</t>
-  </si>
-  <si>
-    <t>NUVAXOVID, dispersion injectable. Vaccin contre la COVID-19 (recombinant avec adjuvant)</t>
-  </si>
-  <si>
     <t>VAC1051</t>
   </si>
   <si>
@@ -669,7 +669,7 @@
     <t>3400930243411</t>
   </si>
   <si>
-    <t>COMIRNATY 30 microgrammes/dose, dispersion injectable.Vaccin à ARNm (à nucléoside modifié) contre la COVID-19 10 flacons multidoses en verre de 6 doses</t>
+    <t>COMIRNATY 30 microgrammes/dose, dispersion injectable.Vaccin à ARNm (à nucléoside modifié) contre la COVID-19 10 flacons multidoses en verre de 6 doses ( abrogée le 12/12/2024)</t>
   </si>
   <si>
     <t>65456578</t>
@@ -681,7 +681,7 @@
     <t>3400930218662</t>
   </si>
   <si>
-    <t>COMIRNATY 30 microgrammes/dose, dispersion à diluer pour dispersion injectable. Vaccin à ARNm (à nucléoside modifié) contre la COVID-19 195 flacons multidoses en verre de 6 doses</t>
+    <t>COMIRNATY 30 microgrammes/dose, dispersion à diluer pour dispersion injectable. Vaccin à ARNm (à nucléoside modifié) contre la COVID-19 195 flacons multidoses en verre de 6 doses ( abrogée le 03/07/2024)</t>
   </si>
   <si>
     <t>60495328</t>
@@ -699,13 +699,13 @@
     <t>3400935166906</t>
   </si>
   <si>
-    <t>ENGERIX B 20 microgrammes/1 ml, suspension injectable en seringue préremplie. Vaccin de l'hépatite B (ADNr), (adsorbé) (VHB) 1 seringue(s) préremplie(s) en verre de 1 ml avec aiguille(s)</t>
+    <t>ENGERIX B 20 microgrammes/1 mL, suspension injectable en seringue préremplie. Vaccin de l'hépatite B (ADNr), (adsorbé) (VHB) 1 seringue(s) préremplie(s) en verre de 1 ml avec aiguille(s)</t>
   </si>
   <si>
     <t>62279329</t>
   </si>
   <si>
-    <t>ENGERIX B 20 microgrammes/1 ml, suspension injectable en seringue préremplie. Vaccin de l'hépatite B (ADNr), (adsorbé) (VHB)</t>
+    <t>ENGERIX B 20 microgrammes/1 mL, suspension injectable en seringue préremplie. Vaccin de l'hépatite B (ADNr), (adsorbé) (VHB)</t>
   </si>
   <si>
     <t>VAC0009</t>
@@ -834,16 +834,16 @@
     <t>COMIRNATY ORIGINAL/OMICRON BA.4-5 (5/5 µg) ENFANT 5-11 ANS BIONTECH-PFIZER</t>
   </si>
   <si>
+    <t>64089816</t>
+  </si>
+  <si>
+    <t>COMIRNATY ORIGINAL/OMICRON BA.4-5 (5/5 microgrammes)/dose, dispersion à diluer pour dispersion injectable. Vaccin à ARNm (à nucléoside modifié) contre la COVID-19</t>
+  </si>
+  <si>
     <t>3400930264478</t>
   </si>
   <si>
-    <t>COMIRNATY ORIGINAL/OMICRON BA.4-5 (5/5 microgrammes)/dose, dispersion à diluer pour dispersion injectable. Vaccin à ARNm (à nucléoside modifié) contre la COVID-19 10 flacon(s) multidose(s) en verre de 10 dose(s)</t>
-  </si>
-  <si>
-    <t>64089816</t>
-  </si>
-  <si>
-    <t>COMIRNATY ORIGINAL/OMICRON BA.4-5 (5/5 microgrammes)/dose, dispersion à diluer pour dispersion injectable. Vaccin à ARNm (à nucléoside modifié) contre la COVID-19</t>
+    <t>COMIRNATY ORIGINAL/OMICRON BA.4-5 (5/5 microgrammes)/dose, dispersion à diluer pour dispersion injectable. Vaccin à ARNm (à nucléoside modifié) contre la COVID-19 10 flacon(s) multidose(s) en verre de 10 dose(s) ( abrogée le 12/12/2024)</t>
   </si>
   <si>
     <t>VAC0037</t>
@@ -876,18 +876,18 @@
     <t>RABIPUR</t>
   </si>
   <si>
+    <t>66800338</t>
+  </si>
+  <si>
+    <t>RABIPUR, poudre et solvant pour solution injectable en seringue préremplie. Vaccin rabique (inactivé)</t>
+  </si>
+  <si>
     <t>3400930071595</t>
   </si>
   <si>
     <t>RABIPUR, poudre et solvant pour solution injectable en seringue préremplie. Vaccin rabique (inactivé) 1 flacon en verre - 1 seringue préremplie en verre de 1 ml et 2 aiguilles séparées</t>
   </si>
   <si>
-    <t>66800338</t>
-  </si>
-  <si>
-    <t>RABIPUR, poudre et solvant pour solution injectable en seringue préremplie. Vaccin rabique (inactivé)</t>
-  </si>
-  <si>
     <t>VAC0060</t>
   </si>
   <si>
@@ -948,18 +948,18 @@
     <t>INFANRIXTETRA</t>
   </si>
   <si>
+    <t>3400935524676</t>
+  </si>
+  <si>
+    <t>INFANRIXTETRA, suspension injectable en seringue préremplie. Vaccin diphtérique, tétanique, coquelucheux acellulaire, poliomyélitique inactivé, adsorbé 1 seringue(s) préremplie(s) en verre de 0,5 ml</t>
+  </si>
+  <si>
     <t>69777706</t>
   </si>
   <si>
     <t>INFANRIXTETRA, suspension injectable en seringue préremplie. Vaccin diphtérique, tétanique, coquelucheux acellulaire, poliomyélitique inactivé, adsorbé</t>
   </si>
   <si>
-    <t>3400935524676</t>
-  </si>
-  <si>
-    <t>INFANRIXTETRA, suspension injectable en seringue préremplie. Vaccin diphtérique, tétanique, coquelucheux acellulaire, poliomyélitique inactivé, adsorbé 1 seringue(s) préremplie(s) en verre de 0,5 ml</t>
-  </si>
-  <si>
     <t>VAC0014</t>
   </si>
   <si>
@@ -1266,18 +1266,18 @@
     <t>BOOSTRIXTETRA</t>
   </si>
   <si>
+    <t>3400936773875</t>
+  </si>
+  <si>
+    <t>BOOSTRIXTETRA, suspension injectable en seringue préremplie. Vaccin diphtérique, tétanique, coquelucheux (acellulaire multicomposé) et poliomyélitique (inactivé), (adsorbé, à teneur réduite en antigènes) 1 seringue(s) préremplie(s) en verre de 0,5 ml avec aiguille(s)</t>
+  </si>
+  <si>
     <t>62404793</t>
   </si>
   <si>
     <t>BOOSTRIXTETRA, suspension injectable en seringue préremplie. Vaccin diphtérique, tétanique, coquelucheux (acellulaire multicomposé) et poliomyélitique (inactivé), (adsorbé, à teneur réduite en antigènes)</t>
   </si>
   <si>
-    <t>3400936773875</t>
-  </si>
-  <si>
-    <t>BOOSTRIXTETRA, suspension injectable en seringue préremplie. Vaccin diphtérique, tétanique, coquelucheux (acellulaire multicomposé) et poliomyélitique (inactivé), (adsorbé, à teneur réduite en antigènes) 1 seringue(s) préremplie(s) en verre de 0,5 ml avec aiguille(s)</t>
-  </si>
-  <si>
     <t>VAC0780</t>
   </si>
   <si>
@@ -1302,16 +1302,16 @@
     <t>VACCIN BCG AJVACCINES</t>
   </si>
   <si>
+    <t>3400936466135</t>
+  </si>
+  <si>
+    <t>VACCIN BCG AJVaccines, poudre et solvant pour suspension injectable. Vaccin BCG, lyophilisé 5 flacon(s) de poudre en verre jaune(brun) - 5 flacon(s) de solvant en verre de 1 ml</t>
+  </si>
+  <si>
     <t>61077869</t>
   </si>
   <si>
-    <t>VACCIN BCG AJVaccines, poudre et solvant pour suspension injectable</t>
-  </si>
-  <si>
-    <t>3400936466135</t>
-  </si>
-  <si>
-    <t>VACCIN BCG AJVaccines, poudre et solvant pour suspension injectable 5 flacon(s) de poudre en verre jaune(brun) - 5 flacon(s) de solvant en verre de 1 ml</t>
+    <t>VACCIN BCG AJVaccines, poudre et solvant pour suspension injectable. Vaccin BCG, lyophilisé</t>
   </si>
   <si>
     <t>VAC0001</t>
@@ -1413,7 +1413,7 @@
     <t>3400930261729</t>
   </si>
   <si>
-    <t>COMIRNATY ORIGINAL/OMICRON BA.1 (15/15 microgrammes)/dose, dispersion injectable. Vaccin à ARNm (à nucléoside modifié) contre la COVID-19 10 flacon(s) multidose(s) en verre de 6 dose(s)</t>
+    <t>COMIRNATY ORIGINAL/OMICRON BA.1 (15/15 microgrammes)/dose, dispersion injectable. Vaccin à ARNm (à nucléoside modifié) contre la COVID-19 10 flacon(s) multidose(s) en verre de 6 dose(s) ( abrogée le 03/07/2024)</t>
   </si>
   <si>
     <t>69401508</t>
@@ -1500,24 +1500,6 @@
     <t>PRIORIX, poudre et solvant pour solution injectable en seringue préremplie. Vaccin rougeoleux, des oreillons et rubéoleux vivant</t>
   </si>
   <si>
-    <t>VAC0016</t>
-  </si>
-  <si>
-    <t>INFLUVAC</t>
-  </si>
-  <si>
-    <t>3400933652166</t>
-  </si>
-  <si>
-    <t>INFLUVAC, suspension injectable en seringue préremplie, vaccin grippal inactivé à antigènes de surface 1 seringue(s) préremplie(s) en verre de 0,5 ml avec aiguille(s)</t>
-  </si>
-  <si>
-    <t>62027876</t>
-  </si>
-  <si>
-    <t>INFLUVAC, suspension injectable en seringue préremplie, vaccin grippal inactivé à antigènes de surface</t>
-  </si>
-  <si>
     <t>VAC0011</t>
   </si>
   <si>
@@ -1668,16 +1650,16 @@
     <t>SPIKEVAX BIVALENT ORIGINAL/OMICRON BA.4-5 25 µg/25 µg MODERNA</t>
   </si>
   <si>
+    <t>3400930266472</t>
+  </si>
+  <si>
+    <t>SPIKEVAX BIVALENT ORIGINAL/OMICRON BA.4-5 25 microgrammes/25 microgrammes, dispersion injectable. Vaccin à ARNm contre la COVID-19 10 flacon(s) unidose(s) en verre (10 doses)</t>
+  </si>
+  <si>
     <t>69556437</t>
   </si>
   <si>
     <t>SPIKEVAX BIVALENT ORIGINAL/OMICRON BA.4-5 25 microgrammes/25 microgrammes, dispersion injectable. Vaccin à ARNm contre la COVID-19</t>
-  </si>
-  <si>
-    <t>3400930266472</t>
-  </si>
-  <si>
-    <t>SPIKEVAX BIVALENT ORIGINAL/OMICRON BA.4-5 25 microgrammes/25 microgrammes, dispersion injectable. Vaccin à ARNm contre la COVID-19 10 flacon(s) unidose(s) en verre (10 doses)</t>
   </si>
   <si>
     <t>VAC0035</t>
@@ -2023,7 +2005,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E191"/>
+  <dimension ref="A1:E189"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -5088,78 +5070,78 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="B181" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="C181" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D181" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="B181" t="s" s="2">
+      <c r="E181" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="C181" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D181" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="E181" t="s" s="2">
-        <v>558</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="C182" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D182" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E182" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="C183" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D183" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E183" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="C184" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D184" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E184" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="C185" t="s" s="2">
         <v>34</v>
@@ -5173,10 +5155,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="C186" t="s" s="2">
         <v>34</v>
@@ -5190,27 +5172,27 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="B187" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="C187" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D187" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="B187" t="s" s="2">
+      <c r="E187" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="C187" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D187" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="E187" t="s" s="2">
-        <v>572</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C188" t="s" s="2">
         <v>34</v>
@@ -5224,10 +5206,10 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C189" t="s" s="2">
         <v>34</v>
@@ -5237,40 +5219,6 @@
       </c>
       <c r="E189" t="s" s="2">
         <v>576</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="B190" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="C190" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D190" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="E190" t="s" s="2">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="B191" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="C191" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D191" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="E191" t="s" s="2">
-        <v>582</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/alignement-nuva-bdpm.xlsx
+++ b/ig/main/alignement-nuva-bdpm.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="581">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.854</t>
+    <t>1.0.870</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11</t>
+    <t>2025-03-06</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -537,13 +537,13 @@
     <t>69544189</t>
   </si>
   <si>
-    <t>NUVAXOVID, dispersion injectable. Vaccin contre la COVID-19 (recombinant avec adjuvant)</t>
+    <t>NUVAXOVID, dispersion injectable. Vaccin contre la COVID-19 (recombinant, avec adjuvant)</t>
   </si>
   <si>
     <t>3400930245774</t>
   </si>
   <si>
-    <t>NUVAXOVID, dispersion injectable. Vaccin contre la COVID-19 (recombinant avec adjuvant) 10 flacons multidoses en verre de 5 mL de 10 doses (100 doses)</t>
+    <t>NUVAXOVID, dispersion injectable. Vaccin contre la COVID-19 (recombinant, avec adjuvant) 10 flacons multidoses en verre de 5 mL de 10 doses (100 doses)</t>
   </si>
   <si>
     <t>VAC1051</t>
@@ -582,18 +582,18 @@
     <t>HAVRIX NOURRISSONS ET ENFANTS 720 U/0,5 mL</t>
   </si>
   <si>
+    <t>60152436</t>
+  </si>
+  <si>
+    <t>HAVRIX NOURRISSONS ET ENFANTS 720 U/0,5 ml, suspension injectable en seringue préremplie. Vaccin de l'hépatite A (inactivé, adsorbé)</t>
+  </si>
+  <si>
     <t>3400934760457</t>
   </si>
   <si>
     <t>HAVRIX NOURRISSONS ET ENFANTS 720 U/0,5 ml, suspension injectable en seringue préremplie. Vaccin de l'hépatite A (inactivé, adsorbé) 1 seringue(s) préremplie(s) en verre de 0,5 ml avec aiguille(s)</t>
   </si>
   <si>
-    <t>60152436</t>
-  </si>
-  <si>
-    <t>HAVRIX NOURRISSONS ET ENFANTS 720 U/0,5 ml, suspension injectable en seringue préremplie. Vaccin de l'hépatite A (inactivé, adsorbé)</t>
-  </si>
-  <si>
     <t>VAC0013</t>
   </si>
   <si>
@@ -844,6 +844,18 @@
   </si>
   <si>
     <t>COMIRNATY ORIGINAL/OMICRON BA.4-5 (5/5 microgrammes)/dose, dispersion à diluer pour dispersion injectable. Vaccin à ARNm (à nucléoside modifié) contre la COVID-19 10 flacon(s) multidose(s) en verre de 10 dose(s) ( abrogée le 12/12/2024)</t>
+  </si>
+  <si>
+    <t>VAC0644</t>
+  </si>
+  <si>
+    <t>QDENGA</t>
+  </si>
+  <si>
+    <t>3400930266458</t>
+  </si>
+  <si>
+    <t>QDENGA, poudre et solvant pour solution injectable en seringue préremplie 1 flacon en verre de 1 dose - 1 seringue préremplie en verre de 0,5 mL + 2 aiguilles</t>
   </si>
   <si>
     <t>VAC0037</t>
@@ -2005,7 +2017,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E189"/>
+  <dimension ref="A1:E190"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -3489,44 +3501,44 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C88" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D88" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E88" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C89" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D89" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E89" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C90" t="s" s="2">
         <v>34</v>
@@ -3540,27 +3552,27 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C91" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E91" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C92" t="s" s="2">
         <v>34</v>
@@ -3574,27 +3586,27 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C93" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D93" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E93" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C94" t="s" s="2">
         <v>34</v>
@@ -3608,27 +3620,27 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C95" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D95" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E95" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C96" t="s" s="2">
         <v>34</v>
@@ -3642,27 +3654,27 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C97" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D97" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E97" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C98" t="s" s="2">
         <v>34</v>
@@ -3676,27 +3688,27 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C99" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D99" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E99" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C100" t="s" s="2">
         <v>34</v>
@@ -3710,27 +3722,27 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C101" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D101" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E101" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C102" t="s" s="2">
         <v>34</v>
@@ -3744,27 +3756,27 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C103" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D103" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E103" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C104" t="s" s="2">
         <v>34</v>
@@ -3778,27 +3790,27 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C105" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D105" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E105" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C106" t="s" s="2">
         <v>34</v>
@@ -3812,44 +3824,44 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C107" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D107" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E107" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C108" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D108" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E108" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C109" t="s" s="2">
         <v>34</v>
@@ -3863,27 +3875,27 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C110" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D110" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E110" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C111" t="s" s="2">
         <v>34</v>
@@ -3897,44 +3909,44 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C112" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D112" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E112" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C113" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D113" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E113" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C114" t="s" s="2">
         <v>34</v>
@@ -3948,27 +3960,27 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C115" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D115" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E115" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C116" t="s" s="2">
         <v>34</v>
@@ -3982,27 +3994,27 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C117" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D117" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E117" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C118" t="s" s="2">
         <v>34</v>
@@ -4016,27 +4028,27 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C119" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D119" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E119" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C120" t="s" s="2">
         <v>34</v>
@@ -4050,27 +4062,27 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C121" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D121" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E121" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C122" t="s" s="2">
         <v>34</v>
@@ -4084,27 +4096,27 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C123" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D123" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E123" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C124" t="s" s="2">
         <v>34</v>
@@ -4118,27 +4130,27 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C125" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D125" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E125" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C126" t="s" s="2">
         <v>34</v>
@@ -4152,27 +4164,27 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C127" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D127" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E127" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C128" t="s" s="2">
         <v>34</v>
@@ -4186,27 +4198,27 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C129" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D129" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E129" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C130" t="s" s="2">
         <v>34</v>
@@ -4220,27 +4232,27 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C131" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D131" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E131" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C132" t="s" s="2">
         <v>34</v>
@@ -4254,27 +4266,27 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C133" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D133" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E133" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C134" t="s" s="2">
         <v>34</v>
@@ -4288,27 +4300,27 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C135" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D135" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E135" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C136" t="s" s="2">
         <v>34</v>
@@ -4322,27 +4334,27 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C137" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D137" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E137" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C138" t="s" s="2">
         <v>34</v>
@@ -4356,27 +4368,27 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C139" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D139" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E139" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C140" t="s" s="2">
         <v>34</v>
@@ -4390,27 +4402,27 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="C141" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D141" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E141" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C142" t="s" s="2">
         <v>34</v>
@@ -4424,27 +4436,27 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C143" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D143" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E143" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C144" t="s" s="2">
         <v>34</v>
@@ -4458,27 +4470,27 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C145" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D145" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E145" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C146" t="s" s="2">
         <v>34</v>
@@ -4492,27 +4504,27 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C147" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D147" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E147" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C148" t="s" s="2">
         <v>34</v>
@@ -4526,27 +4538,27 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C149" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D149" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E149" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C150" t="s" s="2">
         <v>34</v>
@@ -4560,27 +4572,27 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C151" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D151" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E151" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C152" t="s" s="2">
         <v>34</v>
@@ -4594,44 +4606,44 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="C153" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D153" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E153" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="C154" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D154" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E154" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="C155" t="s" s="2">
         <v>34</v>
@@ -4645,27 +4657,27 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C156" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D156" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E156" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C157" t="s" s="2">
         <v>34</v>
@@ -4679,27 +4691,27 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C158" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D158" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E158" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C159" t="s" s="2">
         <v>34</v>
@@ -4713,27 +4725,27 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="C160" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D160" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E160" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C161" t="s" s="2">
         <v>34</v>
@@ -4747,27 +4759,27 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C162" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D162" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E162" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C163" t="s" s="2">
         <v>34</v>
@@ -4781,27 +4793,27 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C164" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D164" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E164" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C165" t="s" s="2">
         <v>34</v>
@@ -4815,27 +4827,27 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="C166" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D166" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E166" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C167" t="s" s="2">
         <v>34</v>
@@ -4849,27 +4861,27 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C168" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D168" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E168" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C169" t="s" s="2">
         <v>34</v>
@@ -4883,27 +4895,27 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C170" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D170" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E170" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C171" t="s" s="2">
         <v>34</v>
@@ -4917,27 +4929,27 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C172" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D172" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E172" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C173" t="s" s="2">
         <v>34</v>
@@ -4951,27 +4963,27 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="C174" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D174" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E174" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C175" t="s" s="2">
         <v>34</v>
@@ -4985,27 +4997,27 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C176" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D176" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E176" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C177" t="s" s="2">
         <v>34</v>
@@ -5019,27 +5031,27 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="C178" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D178" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E178" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C179" t="s" s="2">
         <v>34</v>
@@ -5053,95 +5065,95 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C180" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D180" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E180" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C181" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D181" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="E181" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C182" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D182" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E182" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C183" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D183" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E183" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C184" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D184" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E184" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="C185" t="s" s="2">
         <v>34</v>
@@ -5155,44 +5167,44 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="C186" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D186" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E186" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="C187" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D187" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E187" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="C188" t="s" s="2">
         <v>34</v>
@@ -5206,19 +5218,36 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="C189" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D189" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="E189" t="s" s="2">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="E189" t="s" s="2">
+      <c r="B190" t="s" s="2">
         <v>576</v>
+      </c>
+      <c r="C190" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D190" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="E190" t="s" s="2">
+        <v>580</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/alignement-nuva-bdpm.xlsx
+++ b/ig/main/alignement-nuva-bdpm.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="585">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.870</t>
+    <t>1.0.895</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06</t>
+    <t>2025-04-03</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -168,6 +168,18 @@
     <t>COMIRNATY 3 microgrammes/dose, dispersion à diluer pour dispersion injectable.Vaccin à ARNm (à nucléoside modifié) contre la COVID-19</t>
   </si>
   <si>
+    <t>VAC1055</t>
+  </si>
+  <si>
+    <t>NUVAXOVID XBB.1.5</t>
+  </si>
+  <si>
+    <t>65689785</t>
+  </si>
+  <si>
+    <t>NUVAXOVID XBB.1.5, dispersion injectable. Vaccin contre la COVID-19 (recombinant, avec adjuvant)</t>
+  </si>
+  <si>
     <t>VAC0666</t>
   </si>
   <si>
@@ -354,18 +366,18 @@
     <t>IXIARO</t>
   </si>
   <si>
+    <t>3400939395975</t>
+  </si>
+  <si>
+    <t>IXIARO, suspension injectable. Vaccin de l'encéphalite japonaise (inactivé, adsorbé) 1 seringue(s) préremplie(s) en verre de 0,5 ml</t>
+  </si>
+  <si>
     <t>62816512</t>
   </si>
   <si>
     <t>IXIARO, suspension injectable. Vaccin de l'encéphalite japonaise (inactivé, adsorbé)</t>
   </si>
   <si>
-    <t>3400939395975</t>
-  </si>
-  <si>
-    <t>IXIARO, suspension injectable. Vaccin de l'encéphalite japonaise (inactivé, adsorbé) 1 seringue(s) préremplie(s) en verre de 0,5 ml</t>
-  </si>
-  <si>
     <t>VAC0031</t>
   </si>
   <si>
@@ -582,18 +594,18 @@
     <t>HAVRIX NOURRISSONS ET ENFANTS 720 U/0,5 mL</t>
   </si>
   <si>
+    <t>3400934760457</t>
+  </si>
+  <si>
+    <t>HAVRIX NOURRISSONS ET ENFANTS 720 U/0,5 ml, suspension injectable en seringue préremplie. Vaccin de l'hépatite A (inactivé, adsorbé) 1 seringue(s) préremplie(s) en verre de 0,5 ml avec aiguille(s)</t>
+  </si>
+  <si>
     <t>60152436</t>
   </si>
   <si>
     <t>HAVRIX NOURRISSONS ET ENFANTS 720 U/0,5 ml, suspension injectable en seringue préremplie. Vaccin de l'hépatite A (inactivé, adsorbé)</t>
   </si>
   <si>
-    <t>3400934760457</t>
-  </si>
-  <si>
-    <t>HAVRIX NOURRISSONS ET ENFANTS 720 U/0,5 ml, suspension injectable en seringue préremplie. Vaccin de l'hépatite A (inactivé, adsorbé) 1 seringue(s) préremplie(s) en verre de 0,5 ml avec aiguille(s)</t>
-  </si>
-  <si>
     <t>VAC0013</t>
   </si>
   <si>
@@ -897,7 +909,7 @@
     <t>3400930071595</t>
   </si>
   <si>
-    <t>RABIPUR, poudre et solvant pour solution injectable en seringue préremplie. Vaccin rabique (inactivé) 1 flacon en verre - 1 seringue préremplie en verre de 1 ml et 2 aiguilles séparées</t>
+    <t>RABIPUR, poudre et solvant pour solution injectable en seringue préremplie. Vaccin rabique (inactivé) 1 flacon en verre - 1 seringue préremplie en verre de 1 ml et 2 aiguilles séparées une pour la reconstitution et une pour ladministration</t>
   </si>
   <si>
     <t>VAC0060</t>
@@ -2017,7 +2029,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E190"/>
+  <dimension ref="A1:E191"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2175,44 +2187,44 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>34</v>
@@ -2226,27 +2238,27 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s" s="2">
         <v>34</v>
@@ -2260,61 +2272,61 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s" s="2">
         <v>34</v>
@@ -2328,27 +2340,27 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s" s="2">
         <v>34</v>
@@ -2362,27 +2374,27 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s" s="2">
         <v>34</v>
@@ -2396,27 +2408,27 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s" s="2">
         <v>34</v>
@@ -2430,27 +2442,27 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C25" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C26" t="s" s="2">
         <v>34</v>
@@ -2464,27 +2476,27 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C27" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C28" t="s" s="2">
         <v>34</v>
@@ -2498,27 +2510,27 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C29" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C30" t="s" s="2">
         <v>34</v>
@@ -2532,27 +2544,27 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C31" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C32" t="s" s="2">
         <v>34</v>
@@ -2566,27 +2578,27 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C33" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C34" t="s" s="2">
         <v>34</v>
@@ -2600,27 +2612,27 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C35" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C36" t="s" s="2">
         <v>34</v>
@@ -2634,27 +2646,27 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C37" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C38" t="s" s="2">
         <v>34</v>
@@ -2668,27 +2680,27 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C39" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C40" t="s" s="2">
         <v>34</v>
@@ -2702,27 +2714,27 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C41" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E41" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C42" t="s" s="2">
         <v>34</v>
@@ -2736,78 +2748,78 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C43" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C44" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C45" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C46" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="C47" t="s" s="2">
         <v>34</v>
@@ -2821,27 +2833,27 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C48" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C49" t="s" s="2">
         <v>34</v>
@@ -2855,27 +2867,27 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C50" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C51" t="s" s="2">
         <v>34</v>
@@ -2889,27 +2901,27 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C52" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C53" t="s" s="2">
         <v>34</v>
@@ -2923,27 +2935,27 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C54" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C55" t="s" s="2">
         <v>34</v>
@@ -2974,27 +2986,27 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C57" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E57" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C58" t="s" s="2">
         <v>34</v>
@@ -3008,27 +3020,27 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C59" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E59" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C60" t="s" s="2">
         <v>34</v>
@@ -3042,27 +3054,27 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C61" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E61" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C62" t="s" s="2">
         <v>34</v>
@@ -3076,27 +3088,27 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C63" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C64" t="s" s="2">
         <v>34</v>
@@ -3127,61 +3139,61 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C66" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E66" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C67" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C68" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E68" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C69" t="s" s="2">
         <v>34</v>
@@ -3195,27 +3207,27 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C70" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D70" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E70" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C71" t="s" s="2">
         <v>34</v>
@@ -3229,27 +3241,27 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C72" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C73" t="s" s="2">
         <v>34</v>
@@ -3263,44 +3275,44 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C74" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E74" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C75" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C76" t="s" s="2">
         <v>34</v>
@@ -3314,61 +3326,61 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C77" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E77" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C78" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E78" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C79" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E79" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C80" t="s" s="2">
         <v>34</v>
@@ -3399,27 +3411,27 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C82" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E82" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C83" t="s" s="2">
         <v>34</v>
@@ -3433,27 +3445,27 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C84" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E84" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C85" t="s" s="2">
         <v>34</v>
@@ -3467,27 +3479,27 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C86" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D86" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E86" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C87" t="s" s="2">
         <v>34</v>
@@ -3518,44 +3530,44 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C89" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D89" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E89" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C90" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D90" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E90" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C91" t="s" s="2">
         <v>34</v>
@@ -3569,27 +3581,27 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C92" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D92" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E92" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C93" t="s" s="2">
         <v>34</v>
@@ -3603,27 +3615,27 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C94" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D94" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E94" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C95" t="s" s="2">
         <v>34</v>
@@ -3637,27 +3649,27 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C96" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D96" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E96" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C97" t="s" s="2">
         <v>34</v>
@@ -3671,27 +3683,27 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C98" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D98" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E98" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C99" t="s" s="2">
         <v>34</v>
@@ -3705,27 +3717,27 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C100" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D100" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E100" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C101" t="s" s="2">
         <v>34</v>
@@ -3739,27 +3751,27 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C102" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D102" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E102" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C103" t="s" s="2">
         <v>34</v>
@@ -3773,27 +3785,27 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C104" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D104" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E104" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C105" t="s" s="2">
         <v>34</v>
@@ -3807,27 +3819,27 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C106" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D106" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E106" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C107" t="s" s="2">
         <v>34</v>
@@ -3841,44 +3853,44 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C108" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D108" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E108" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C109" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D109" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E109" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C110" t="s" s="2">
         <v>34</v>
@@ -3892,27 +3904,27 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C111" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D111" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E111" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C112" t="s" s="2">
         <v>34</v>
@@ -3926,44 +3938,44 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C113" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D113" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E113" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C114" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D114" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E114" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C115" t="s" s="2">
         <v>34</v>
@@ -3977,27 +3989,27 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C116" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D116" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E116" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C117" t="s" s="2">
         <v>34</v>
@@ -4011,27 +4023,27 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C118" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D118" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E118" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C119" t="s" s="2">
         <v>34</v>
@@ -4045,27 +4057,27 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C120" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D120" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E120" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C121" t="s" s="2">
         <v>34</v>
@@ -4079,27 +4091,27 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C122" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D122" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E122" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C123" t="s" s="2">
         <v>34</v>
@@ -4113,27 +4125,27 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C124" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D124" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E124" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C125" t="s" s="2">
         <v>34</v>
@@ -4147,27 +4159,27 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C126" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D126" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E126" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C127" t="s" s="2">
         <v>34</v>
@@ -4181,27 +4193,27 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C128" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D128" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E128" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C129" t="s" s="2">
         <v>34</v>
@@ -4215,27 +4227,27 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C130" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D130" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E130" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C131" t="s" s="2">
         <v>34</v>
@@ -4249,27 +4261,27 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C132" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D132" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E132" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C133" t="s" s="2">
         <v>34</v>
@@ -4283,27 +4295,27 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C134" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D134" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E134" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C135" t="s" s="2">
         <v>34</v>
@@ -4317,27 +4329,27 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C136" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D136" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E136" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C137" t="s" s="2">
         <v>34</v>
@@ -4351,27 +4363,27 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C138" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D138" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E138" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C139" t="s" s="2">
         <v>34</v>
@@ -4385,27 +4397,27 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C140" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D140" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E140" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C141" t="s" s="2">
         <v>34</v>
@@ -4419,27 +4431,27 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C142" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D142" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E142" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C143" t="s" s="2">
         <v>34</v>
@@ -4453,27 +4465,27 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C144" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D144" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E144" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C145" t="s" s="2">
         <v>34</v>
@@ -4487,27 +4499,27 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C146" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D146" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E146" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C147" t="s" s="2">
         <v>34</v>
@@ -4521,27 +4533,27 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C148" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D148" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E148" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C149" t="s" s="2">
         <v>34</v>
@@ -4555,27 +4567,27 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C150" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D150" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E150" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C151" t="s" s="2">
         <v>34</v>
@@ -4589,27 +4601,27 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="C152" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D152" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E152" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C153" t="s" s="2">
         <v>34</v>
@@ -4623,44 +4635,44 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C154" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D154" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E154" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C155" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D155" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E155" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="C156" t="s" s="2">
         <v>34</v>
@@ -4674,27 +4686,27 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C157" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D157" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E157" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C158" t="s" s="2">
         <v>34</v>
@@ -4708,27 +4720,27 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C159" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D159" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E159" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C160" t="s" s="2">
         <v>34</v>
@@ -4742,27 +4754,27 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="C161" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D161" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E161" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C162" t="s" s="2">
         <v>34</v>
@@ -4776,27 +4788,27 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C163" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D163" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E163" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C164" t="s" s="2">
         <v>34</v>
@@ -4810,27 +4822,27 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="C165" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D165" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E165" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C166" t="s" s="2">
         <v>34</v>
@@ -4844,27 +4856,27 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C167" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D167" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E167" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C168" t="s" s="2">
         <v>34</v>
@@ -4878,27 +4890,27 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="C169" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D169" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E169" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C170" t="s" s="2">
         <v>34</v>
@@ -4912,27 +4924,27 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C171" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D171" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E171" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C172" t="s" s="2">
         <v>34</v>
@@ -4946,27 +4958,27 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C173" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D173" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E173" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C174" t="s" s="2">
         <v>34</v>
@@ -4980,27 +4992,27 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C175" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D175" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E175" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C176" t="s" s="2">
         <v>34</v>
@@ -5014,27 +5026,27 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C177" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D177" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E177" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C178" t="s" s="2">
         <v>34</v>
@@ -5048,27 +5060,27 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="C179" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D179" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E179" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C180" t="s" s="2">
         <v>34</v>
@@ -5082,95 +5094,95 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C181" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D181" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E181" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C182" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D182" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E182" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C183" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D183" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E183" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C184" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D184" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="E184" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C185" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D185" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E185" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="C186" t="s" s="2">
         <v>34</v>
@@ -5184,44 +5196,44 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="C187" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D187" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E187" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="C188" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D188" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E188" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="C189" t="s" s="2">
         <v>34</v>
@@ -5235,19 +5247,36 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="C190" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D190" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="E190" t="s" s="2">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="E190" t="s" s="2">
+      <c r="B191" t="s" s="2">
         <v>580</v>
+      </c>
+      <c r="C191" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D191" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="E191" t="s" s="2">
+        <v>584</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/alignement-nuva-bdpm.xlsx
+++ b/ig/main/alignement-nuva-bdpm.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="587">
   <si>
     <t>Property</t>
   </si>
@@ -70,6 +70,12 @@
   </si>
   <si>
     <t>null (https://smt.esante.gouv.fr/fhir/ConceptMap/alignement-nuva-bdpm)</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
@@ -1901,7 +1907,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -1998,21 +2004,21 @@
       <c r="A12" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B14" t="s" s="2">
         <v>24</v>
       </c>
+      <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
@@ -2020,6 +2026,14 @@
       </c>
       <c r="B15" t="s" s="2">
         <v>26</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -2034,3249 +2048,3249 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="C1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>25</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E41" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E42" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E56" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E57" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E59" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E60" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E61" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E66" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E68" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D69" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E69" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D70" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E70" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E71" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E74" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E76" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E77" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E78" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E79" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E80" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E82" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D83" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E83" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E84" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E85" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D86" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E86" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E87" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D88" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E88" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D89" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E89" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D90" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E90" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E91" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D92" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E92" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D93" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E93" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D94" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E94" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D95" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E95" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D96" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E96" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D97" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E97" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D98" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E98" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D99" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E99" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D100" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E100" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D101" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E101" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D102" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E102" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D103" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E103" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D104" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E104" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D105" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E105" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D106" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E106" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D107" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E107" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D108" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E108" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D109" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E109" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D110" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E110" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D111" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E111" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D112" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E112" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D113" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E113" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D114" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E114" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D115" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E115" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D116" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E116" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D117" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E117" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D118" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E118" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D119" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E119" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D120" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E120" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D121" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E121" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D122" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E122" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D123" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E123" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D124" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E124" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D125" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E125" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D126" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E126" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D127" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E127" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D128" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E128" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D129" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E129" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D130" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E130" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D131" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E131" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D132" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E132" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D133" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E133" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D134" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E134" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D135" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E135" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D136" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E136" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D137" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E137" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D138" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E138" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D139" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E139" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D140" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E140" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D141" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E141" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D142" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E142" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D143" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E143" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D144" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E144" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D145" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E145" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D146" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E146" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D147" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E147" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D148" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E148" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D149" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E149" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D150" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E150" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D151" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E151" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D152" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E152" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D153" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E153" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D154" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E154" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D155" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E155" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D156" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E156" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D157" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E157" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D158" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E158" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D159" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E159" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D160" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E160" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D161" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E161" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D162" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E162" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D163" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E163" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D164" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E164" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D165" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E165" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D166" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E166" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D167" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E167" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D168" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E168" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D169" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E169" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D170" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="E170" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D171" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E171" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D172" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E172" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D173" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E173" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D174" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E174" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D175" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E175" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D176" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E176" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D177" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E177" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D178" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="E178" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D179" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E179" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D180" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="E180" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D181" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E181" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D182" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E182" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D183" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="E183" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D184" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E184" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D185" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E185" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D186" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E186" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D187" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E187" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D188" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="E188" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D189" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E189" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D190" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="E190" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D191" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E191" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/alignement-nuva-bdpm.xlsx
+++ b/ig/main/alignement-nuva-bdpm.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="603">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.895</t>
+    <t>1.0.923</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-03</t>
+    <t>2025-05-07</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -120,7 +120,7 @@
     <t>VAC1259</t>
   </si>
   <si>
-    <t>COMIRNATY JN.1 10 µg ENFANT (5-11 ANS)</t>
+    <t>COMIRNATY JN.1 10 µg</t>
   </si>
   <si>
     <t>equivalent</t>
@@ -180,6 +180,12 @@
     <t>NUVAXOVID XBB.1.5</t>
   </si>
   <si>
+    <t>3400930277409</t>
+  </si>
+  <si>
+    <t>NUVAXOVID XBB.1.5, dispersion injectable. Vaccin contre la COVID-19 (recombinant, avec adjuvant) 2 flacons multidoses en verre de 2,5 mL de 5 doses (10 doses)</t>
+  </si>
+  <si>
     <t>65689785</t>
   </si>
   <si>
@@ -189,7 +195,7 @@
     <t>VAC0666</t>
   </si>
   <si>
-    <t>JCOVDEN - COVID-19 VACCINE JANSSEN</t>
+    <t>JCOVDEN</t>
   </si>
   <si>
     <t>3400930222232</t>
@@ -351,7 +357,7 @@
     <t>VAC0833</t>
   </si>
   <si>
-    <t>COMIRNATY 10 µg ENFANT 5-11 ANS BIONTECH-PFIZER</t>
+    <t>COMIRNATY 10 µg BIONTECH-PFIZER</t>
   </si>
   <si>
     <t>69174918</t>
@@ -384,6 +390,18 @@
     <t>IXIARO, suspension injectable. Vaccin de l'encéphalite japonaise (inactivé, adsorbé)</t>
   </si>
   <si>
+    <t>VAC0778</t>
+  </si>
+  <si>
+    <t>VAXCHORA</t>
+  </si>
+  <si>
+    <t>3400930264966</t>
+  </si>
+  <si>
+    <t>VAXCHORA, poudre effervescente et poudre pour suspension buvable. Vaccin anticholérique (vivant,recombiné,orale) 1 sachet(s) papier polyéthylène basse densité (PEBD) aluminium - 1 sachet(s) papier aluminium polyéthylène basse densité (PEBD)</t>
+  </si>
+  <si>
     <t>VAC0031</t>
   </si>
   <si>
@@ -405,7 +423,7 @@
     <t>VAC0166</t>
   </si>
   <si>
-    <t>VAQTA  50 U</t>
+    <t>VAQTA 50 U</t>
   </si>
   <si>
     <t>3400938309959</t>
@@ -477,7 +495,7 @@
     <t>VAC0579</t>
   </si>
   <si>
-    <t>CLAIRYG 50 mg/ml</t>
+    <t>CLAIRYG 50 mg/mL</t>
   </si>
   <si>
     <t>3400957619046</t>
@@ -552,22 +570,22 @@
     <t>NUVAXOVID</t>
   </si>
   <si>
+    <t>3400930245774</t>
+  </si>
+  <si>
+    <t>NUVAXOVID, dispersion injectable. Vaccin contre la COVID-19 (recombinant, avec adjuvant) 10 flacons multidoses en verre de 5 mL de 10 doses (100 doses)</t>
+  </si>
+  <si>
     <t>69544189</t>
   </si>
   <si>
     <t>NUVAXOVID, dispersion injectable. Vaccin contre la COVID-19 (recombinant, avec adjuvant)</t>
   </si>
   <si>
-    <t>3400930245774</t>
-  </si>
-  <si>
-    <t>NUVAXOVID, dispersion injectable. Vaccin contre la COVID-19 (recombinant, avec adjuvant) 10 flacons multidoses en verre de 5 mL de 10 doses (100 doses)</t>
-  </si>
-  <si>
     <t>VAC1051</t>
   </si>
   <si>
-    <t>PFIZER COMIRNATY-30 XBB.1.5 ADULTE (+ 12 ANS)</t>
+    <t>PFIZER COMIRNATY-30 XBB.1.5</t>
   </si>
   <si>
     <t>3400930279038</t>
@@ -597,19 +615,19 @@
     <t>VAC0050</t>
   </si>
   <si>
-    <t>HAVRIX NOURRISSONS ET ENFANTS 720 U/0,5 mL</t>
+    <t>HAVRIX 720 U/0,5 mL</t>
   </si>
   <si>
     <t>3400934760457</t>
   </si>
   <si>
-    <t>HAVRIX NOURRISSONS ET ENFANTS 720 U/0,5 ml, suspension injectable en seringue préremplie. Vaccin de l'hépatite A (inactivé, adsorbé) 1 seringue(s) préremplie(s) en verre de 0,5 ml avec aiguille(s)</t>
+    <t>HAVRIX NOURRISSONS ET ENFANTS 720 U/0,5 mL, suspension injectable en seringue préremplie. Vaccin de l'hépatite A (inactivé, adsorbé) 1 seringue(s) préremplie(s) en verre de 0,5 ml avec aiguille(s)</t>
   </si>
   <si>
     <t>60152436</t>
   </si>
   <si>
-    <t>HAVRIX NOURRISSONS ET ENFANTS 720 U/0,5 ml, suspension injectable en seringue préremplie. Vaccin de l'hépatite A (inactivé, adsorbé)</t>
+    <t>HAVRIX NOURRISSONS ET ENFANTS 720 U/0,5 mL, suspension injectable en seringue préremplie. Vaccin de l'hépatite A (inactivé, adsorbé)</t>
   </si>
   <si>
     <t>VAC0013</t>
@@ -813,7 +831,7 @@
     <t>VAC1260</t>
   </si>
   <si>
-    <t>COMIRNATY JN.1 3 µg ENFANT (6 MOIS-4 ANS)</t>
+    <t>COMIRNATY JN.1 3 µg</t>
   </si>
   <si>
     <t>65290793</t>
@@ -831,7 +849,7 @@
     <t>VAC0649</t>
   </si>
   <si>
-    <t>EFLUELDA TETRA</t>
+    <t>EFLUELDA QIV-HD</t>
   </si>
   <si>
     <t>67823603</t>
@@ -846,10 +864,28 @@
     <t>EFLUELDA TETRA, suspension injectable en seringue préremplie Vaccin grippal quadrivalent (inactivé, à virion fragmenté), 60 microgrammes HA/souche 1 seringue préremplie en verre de 0,7 ml avec aiguille séparée, munie dun bouchon-piston (Bromobutyle) et dun capuchon de protection</t>
   </si>
   <si>
+    <t>VAC0079</t>
+  </si>
+  <si>
+    <t>ENCEPUR</t>
+  </si>
+  <si>
+    <t>3400936774537</t>
+  </si>
+  <si>
+    <t>ENCEPUR 1,5 microgrammes/0,5 ml, suspension injectable en seringue préremplie. Vaccin de l'encéphalite à tiques (inactivé, adsorbé) 1 seringue(s) préremplie(s) en verre de 0,5 ml avec aiguille attachée</t>
+  </si>
+  <si>
+    <t>3400930198391</t>
+  </si>
+  <si>
+    <t>ENCEPUR 1,5 microgrammes/0,5 ml, suspension injectable en seringue préremplie. Vaccin de l'encéphalite à tiques (inactivé, adsorbé) 1 seringue(s) préremplie(s) en verre de 0,5 ml avec aiguille(s) séparée</t>
+  </si>
+  <si>
     <t>VAC1033</t>
   </si>
   <si>
-    <t>COMIRNATY ORIGINAL/OMICRON BA.4-5 (5/5 µg) ENFANT 5-11 ANS BIONTECH-PFIZER</t>
+    <t>COMIRNATY ORIGINAL/OMICRON BA.4-5 (5/5 µg) BIONTECH-PFIZER</t>
   </si>
   <si>
     <t>64089816</t>
@@ -957,7 +993,7 @@
     <t>VAC1052</t>
   </si>
   <si>
-    <t>PFIZER COMIRNATY-10 XBB.1.5 ENFANT (5-11 ANS)</t>
+    <t>PFIZER COMIRNATY-10 XBB.1.5</t>
   </si>
   <si>
     <t>3400930279069</t>
@@ -1071,7 +1107,7 @@
     <t>VAC0038</t>
   </si>
   <si>
-    <t>TICOVAC 0,5 ml ADULTES</t>
+    <t>TICOVAC 0,5 mL</t>
   </si>
   <si>
     <t>3400927841705</t>
@@ -1167,7 +1203,7 @@
     <t>VAC1053</t>
   </si>
   <si>
-    <t>PFIZER COMIRNATY-3 XBB.1.5 ENFANT (6 MOIS-4 ANS)</t>
+    <t>PFIZER COMIRNATY-3 XBB.1.5</t>
   </si>
   <si>
     <t>64995124</t>
@@ -1185,7 +1221,7 @@
     <t>VAC0057</t>
   </si>
   <si>
-    <t>TWINRIX ADULTE</t>
+    <t>TWINRIX 20 µg</t>
   </si>
   <si>
     <t>3400935676931</t>
@@ -1365,7 +1401,7 @@
     <t>VAC0039</t>
   </si>
   <si>
-    <t>TICOVAC 0,25 ml ENFANTS</t>
+    <t>TICOVAC 0,25 mL</t>
   </si>
   <si>
     <t>61440306</t>
@@ -1419,7 +1455,7 @@
     <t>VAC1258</t>
   </si>
   <si>
-    <t>COMIRNATY JN.1 30 µg ADULTE (+ 12 ANS)</t>
+    <t>COMIRNATY JN.1 30 µg</t>
   </si>
   <si>
     <t>3400930299760</t>
@@ -1497,7 +1533,7 @@
     <t>VAC0058</t>
   </si>
   <si>
-    <t>TWINRIX ENFANT</t>
+    <t>TWINRIX 10 µg</t>
   </si>
   <si>
     <t>3400935676870</t>
@@ -1602,22 +1638,34 @@
     <t>SPIKEVAX 0,2 mg/mL, dispersion injectable. Vaccin à ARNm contre la COVID-19</t>
   </si>
   <si>
+    <t>VAC1040</t>
+  </si>
+  <si>
+    <t>AREXVY</t>
+  </si>
+  <si>
+    <t>3400930274170</t>
+  </si>
+  <si>
+    <t>AREXVY, poudre et suspension pour suspension injectable. Vaccin du Virus Respiratoire Syncytial (VRS) (recombinant, avec adjuvant) 1 flacon en verre de 120 microgrammes de poudre - 1 flacon en verre de 0,5 ml de suspension</t>
+  </si>
+  <si>
     <t>VAC0049</t>
   </si>
   <si>
-    <t>HAVRIX 1440 U/1mL ADULTES</t>
+    <t>HAVRIX 1440 U/1mL</t>
   </si>
   <si>
     <t>60386414</t>
   </si>
   <si>
-    <t>HAVRIX 1440 U/1 ml ADULTES, suspension injectable en seringue préremplie. Vaccin de l'hépatite A (inactivé, adsorbé)</t>
+    <t>HAVRIX 1440 U/1 mL ADULTES, suspension injectable en seringue préremplie. Vaccin de l'hépatite A (inactivé, adsorbé)</t>
   </si>
   <si>
     <t>3400933775155</t>
   </si>
   <si>
-    <t>HAVRIX 1440 U/1 ml ADULTES, suspension injectable en seringue préremplie. Vaccin de l'hépatite A (inactivé, adsorbé) 1 seringue(s) préremplie(s) en verre de 1 ml avec aiguille(s)</t>
+    <t>HAVRIX 1440 U/1 mL ADULTES, suspension injectable en seringue préremplie. Vaccin de l'hépatite A (inactivé, adsorbé) 1 seringue(s) préremplie(s) en verre de 1 ml avec aiguille(s)</t>
   </si>
   <si>
     <t>VAC0044</t>
@@ -2043,7 +2091,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E191"/>
+  <dimension ref="A1:E196"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2201,27 +2249,27 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s" s="2">
         <v>57</v>
       </c>
-      <c r="B10" t="s" s="2">
+      <c r="E10" t="s" s="2">
         <v>58</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="E10" t="s" s="2">
-        <v>60</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>36</v>
@@ -2235,10 +2283,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>36</v>
@@ -2252,27 +2300,27 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D13" t="s" s="2">
         <v>65</v>
       </c>
-      <c r="B13" t="s" s="2">
+      <c r="E13" t="s" s="2">
         <v>66</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="E13" t="s" s="2">
-        <v>68</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s" s="2">
         <v>36</v>
@@ -2286,27 +2334,27 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D15" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="B15" t="s" s="2">
+      <c r="E15" t="s" s="2">
         <v>72</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="D15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E15" t="s" s="2">
-        <v>74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s" s="2">
         <v>36</v>
@@ -2320,10 +2368,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s" s="2">
         <v>36</v>
@@ -2337,10 +2385,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s" s="2">
         <v>36</v>
@@ -2354,27 +2402,27 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D19" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="B19" t="s" s="2">
+      <c r="E19" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="D19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E19" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s" s="2">
         <v>36</v>
@@ -2388,27 +2436,27 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D21" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="B21" t="s" s="2">
+      <c r="E21" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="D21" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="E21" t="s" s="2">
-        <v>90</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s" s="2">
         <v>36</v>
@@ -2422,27 +2470,27 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D23" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="B23" t="s" s="2">
+      <c r="E23" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="D23" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="E23" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C24" t="s" s="2">
         <v>36</v>
@@ -2456,27 +2504,27 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D25" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="B25" t="s" s="2">
+      <c r="E25" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="D25" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="E25" t="s" s="2">
-        <v>102</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C26" t="s" s="2">
         <v>36</v>
@@ -2490,27 +2538,27 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D27" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="B27" t="s" s="2">
+      <c r="E27" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="D27" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="E27" t="s" s="2">
-        <v>108</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C28" t="s" s="2">
         <v>36</v>
@@ -2524,27 +2572,27 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D29" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="B29" t="s" s="2">
+      <c r="E29" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="D29" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="E29" t="s" s="2">
-        <v>114</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C30" t="s" s="2">
         <v>36</v>
@@ -2558,27 +2606,27 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D31" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="B31" t="s" s="2">
+      <c r="E31" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="D31" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="E31" t="s" s="2">
-        <v>120</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C32" t="s" s="2">
         <v>36</v>
@@ -2592,27 +2640,27 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D33" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="B33" t="s" s="2">
+      <c r="E33" t="s" s="2">
         <v>124</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="D33" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="E33" t="s" s="2">
-        <v>126</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C34" t="s" s="2">
         <v>36</v>
@@ -2796,61 +2844,61 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C45" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C46" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C47" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C48" t="s" s="2">
         <v>36</v>
@@ -2864,10 +2912,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C49" t="s" s="2">
         <v>36</v>
@@ -3000,27 +3048,27 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D57" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="B57" t="s" s="2">
+      <c r="E57" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="D57" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="E57" t="s" s="2">
-        <v>196</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C58" t="s" s="2">
         <v>36</v>
@@ -3153,27 +3201,27 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D66" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="B66" t="s" s="2">
+      <c r="E66" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="D66" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="E66" t="s" s="2">
-        <v>224</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C67" t="s" s="2">
         <v>36</v>
@@ -3187,44 +3235,44 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C68" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E68" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C69" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D69" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E69" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C70" t="s" s="2">
         <v>36</v>
@@ -3238,10 +3286,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C71" t="s" s="2">
         <v>36</v>
@@ -3323,27 +3371,27 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="C76" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E76" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C77" t="s" s="2">
         <v>36</v>
@@ -3357,10 +3405,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C78" t="s" s="2">
         <v>36</v>
@@ -3374,44 +3422,44 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C79" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E79" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C80" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E80" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C81" t="s" s="2">
         <v>36</v>
@@ -3425,27 +3473,27 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="C82" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D82" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="B82" t="s" s="2">
+      <c r="E82" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="C82" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="D82" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="E82" t="s" s="2">
-        <v>268</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C83" t="s" s="2">
         <v>36</v>
@@ -3544,27 +3592,27 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="C89" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D89" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="B89" t="s" s="2">
+      <c r="E89" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="C89" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="D89" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="E89" t="s" s="2">
-        <v>290</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C90" t="s" s="2">
         <v>36</v>
@@ -3578,10 +3626,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C91" t="s" s="2">
         <v>36</v>
@@ -3612,27 +3660,27 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C93" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D93" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E93" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C94" t="s" s="2">
         <v>36</v>
@@ -3646,10 +3694,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C95" t="s" s="2">
         <v>36</v>
@@ -3901,27 +3949,27 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="C110" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D110" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E110" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C111" t="s" s="2">
         <v>36</v>
@@ -3935,27 +3983,27 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C112" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D112" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E112" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C113" t="s" s="2">
         <v>36</v>
@@ -3969,10 +4017,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C114" t="s" s="2">
         <v>36</v>
@@ -3986,27 +4034,27 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C115" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D115" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E115" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C116" t="s" s="2">
         <v>36</v>
@@ -4020,27 +4068,27 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C117" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D117" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E117" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C118" t="s" s="2">
         <v>36</v>
@@ -4054,10 +4102,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C119" t="s" s="2">
         <v>36</v>
@@ -4683,27 +4731,27 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="C156" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D156" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E156" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C157" t="s" s="2">
         <v>36</v>
@@ -4717,27 +4765,27 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C158" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D158" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E158" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C159" t="s" s="2">
         <v>36</v>
@@ -4751,10 +4799,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C160" t="s" s="2">
         <v>36</v>
@@ -5023,27 +5071,27 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C176" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D176" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E176" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C177" t="s" s="2">
         <v>36</v>
@@ -5057,27 +5105,27 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="C178" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D178" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E178" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C179" t="s" s="2">
         <v>36</v>
@@ -5091,27 +5139,27 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C180" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D180" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E180" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C181" t="s" s="2">
         <v>36</v>
@@ -5125,172 +5173,257 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C182" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D182" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="E182" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C183" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D183" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E183" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>559</v>
+        <v>569</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="C184" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D184" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="E184" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>559</v>
+        <v>569</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="C185" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D185" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="E185" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>559</v>
+        <v>575</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>560</v>
+        <v>576</v>
       </c>
       <c r="C186" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D186" t="s" s="2">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="E186" t="s" s="2">
-        <v>572</v>
+        <v>578</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C187" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D187" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="E187" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C188" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D188" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="E188" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C189" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D189" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="E189" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="C190" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D190" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E190" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="C191" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D191" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="E191" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="B192" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="C192" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D192" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="E192" t="s" s="2">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="B193" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="C193" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D193" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="E193" t="s" s="2">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="B194" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="C194" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D194" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="E194" t="s" s="2">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="B195" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="C195" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D195" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="E195" t="s" s="2">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="B196" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="C196" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D196" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="E196" t="s" s="2">
+        <v>602</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/alignement-nuva-bdpm.xlsx
+++ b/ig/main/alignement-nuva-bdpm.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="604">
   <si>
     <t>Property</t>
   </si>
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ConceptMap/alignement-nuva-bdpm</t>
+    <t>https://smt-pprod.esante.gouv.fr/fhir/ConceptMap/alignement-nuva-bdpm</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.923</t>
+    <t>1.0.930</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-07</t>
+    <t>2025-06-05</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>null (https://smt.esante.gouv.fr/fhir/ConceptMap/alignement-nuva-bdpm)</t>
+    <t>null (https://smt-pprod.esante.gouv.fr/fhir/ConceptMap/alignement-nuva-bdpm)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -90,16 +90,19 @@
     <t>Copyright</t>
   </si>
   <si>
+    <t>[SYADEM](https://data.esante.gouv.fr/profile/distributions/licenceNuva)</t>
+  </si>
+  <si>
     <t>Source</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/terminologie-nuva?vs</t>
+    <t>https://smt-pprod.esante.gouv.fr/terminologie-nuva?vs</t>
   </si>
   <si>
     <t>Target</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/terminologie-bdpm?vs</t>
+    <t>https://smt-pprod.esante.gouv.fr/terminologie-bdpm?vs</t>
   </si>
   <si>
     <t>Display</t>
@@ -108,13 +111,13 @@
     <t>Relationship</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/terminologie-nuva</t>
+    <t>https://smt-pprod.esante.gouv.fr/terminologie-nuva</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/terminologie-bdpm</t>
+    <t>https://smt-pprod.esante.gouv.fr/terminologie-bdpm</t>
   </si>
   <si>
     <t>VAC1259</t>
@@ -2066,22 +2069,24 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -2096,3334 +2101,3334 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C1" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>30</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E2" t="s" s="2">
         <v>33</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E41" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E42" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E56" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E57" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E59" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E60" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E61" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E66" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E68" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D69" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E69" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D70" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E70" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E71" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E74" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E76" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E77" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E78" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E79" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E80" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E82" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D83" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E83" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E84" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E85" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D86" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E86" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E87" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D88" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E88" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D89" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E89" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D90" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E90" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E91" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D92" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E92" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D93" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E93" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D94" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E94" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D95" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E95" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D96" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E96" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D97" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E97" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D98" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E98" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D99" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E99" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D100" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E100" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D101" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E101" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D102" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E102" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D103" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E103" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D104" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E104" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D105" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E105" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D106" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E106" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D107" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E107" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D108" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E108" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D109" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E109" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D110" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E110" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D111" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E111" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D112" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E112" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D113" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E113" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D114" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E114" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D115" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E115" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D116" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E116" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D117" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E117" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D118" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E118" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D119" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E119" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D120" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E120" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D121" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E121" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D122" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E122" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D123" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E123" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D124" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E124" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D125" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E125" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D126" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E126" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D127" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E127" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D128" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E128" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D129" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E129" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D130" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E130" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D131" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E131" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D132" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E132" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D133" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E133" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D134" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E134" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D135" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E135" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D136" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E136" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D137" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E137" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D138" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E138" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D139" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E139" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D140" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E140" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D141" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E141" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D142" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E142" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D143" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E143" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D144" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E144" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D145" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E145" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D146" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E146" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D147" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E147" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D148" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E148" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D149" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E149" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D150" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E150" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D151" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E151" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D152" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E152" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D153" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E153" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D154" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E154" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D155" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E155" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D156" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E156" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D157" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E157" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D158" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E158" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D159" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E159" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D160" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E160" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D161" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E161" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D162" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E162" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D163" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E163" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D164" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E164" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D165" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E165" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D166" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E166" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D167" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E167" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D168" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E168" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D169" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E169" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D170" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E170" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D171" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E171" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D172" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E172" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D173" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E173" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D174" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E174" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D175" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E175" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D176" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E176" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D177" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E177" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D178" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E178" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D179" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E179" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D180" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E180" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D181" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E181" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D182" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E182" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D183" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E183" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D184" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E184" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D185" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E185" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D186" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E186" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D187" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E187" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D188" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E188" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D189" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E189" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D190" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E190" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D191" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E191" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D192" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E192" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D193" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E193" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D194" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E194" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D195" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E195" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D196" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E196" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/alignement-nuva-bdpm.xlsx
+++ b/ig/main/alignement-nuva-bdpm.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="603">
   <si>
     <t>Property</t>
   </si>
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://smt-pprod.esante.gouv.fr/fhir/ConceptMap/alignement-nuva-bdpm</t>
+    <t>https://smt.esante.gouv.fr/fhir/ConceptMap/alignement-nuva-bdpm</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.930</t>
+    <t>1.0.939</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-05</t>
+    <t>2025-07-03</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>null (https://smt-pprod.esante.gouv.fr/fhir/ConceptMap/alignement-nuva-bdpm)</t>
+    <t>null (https://smt.esante.gouv.fr/fhir/ConceptMap/alignement-nuva-bdpm)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -90,19 +90,16 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>[SYADEM](https://data.esante.gouv.fr/profile/distributions/licenceNuva)</t>
-  </si>
-  <si>
     <t>Source</t>
   </si>
   <si>
-    <t>https://smt-pprod.esante.gouv.fr/terminologie-nuva?vs</t>
+    <t>https://smt.esante.gouv.fr/terminologie-nuva?vs</t>
   </si>
   <si>
     <t>Target</t>
   </si>
   <si>
-    <t>https://smt-pprod.esante.gouv.fr/terminologie-bdpm?vs</t>
+    <t>https://smt.esante.gouv.fr/terminologie-bdpm?vs</t>
   </si>
   <si>
     <t>Display</t>
@@ -111,13 +108,13 @@
     <t>Relationship</t>
   </si>
   <si>
-    <t>https://smt-pprod.esante.gouv.fr/terminologie-nuva</t>
+    <t>https://smt.esante.gouv.fr/terminologie-nuva</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://smt-pprod.esante.gouv.fr/terminologie-bdpm</t>
+    <t>https://smt.esante.gouv.fr/terminologie-bdpm</t>
   </si>
   <si>
     <t>VAC1259</t>
@@ -432,13 +429,13 @@
     <t>3400938309959</t>
   </si>
   <si>
-    <t>VAQTA 50 U/1 ml, suspension injectable en seringue préremplie. Vaccin de lhépatite A, inactivé, adsorbé. Pour adultes 1 seringue(s) préremplie(s) en verre de 1 ml munie d'un bouchon-piston, d'un protège-embout, avec 2 aiguille(s) séparées</t>
+    <t>VAQTA 50 U/1 ml, suspension injectable en seringue préremplie. Vaccin de l'hépatite A, inactivé, adsorbé. Pour adultes 1 seringue(s) préremplie(s) en verre de 1 ml munie d'un bouchon-piston, d'un protège-embout, avec 2 aiguille(s) séparées</t>
   </si>
   <si>
     <t>62087670</t>
   </si>
   <si>
-    <t>VAQTA 50 U/1 ml, suspension injectable en seringue préremplie. Vaccin de lhépatite A, inactivé, adsorbé. Pour adultes</t>
+    <t>VAQTA 50 U/1 ml, suspension injectable en seringue préremplie. Vaccin de l'hépatite A, inactivé, adsorbé. Pour adultes</t>
   </si>
   <si>
     <t>VAC0161</t>
@@ -864,7 +861,7 @@
     <t>3400930205402</t>
   </si>
   <si>
-    <t>EFLUELDA TETRA, suspension injectable en seringue préremplie Vaccin grippal quadrivalent (inactivé, à virion fragmenté), 60 microgrammes HA/souche 1 seringue préremplie en verre de 0,7 ml avec aiguille séparée, munie dun bouchon-piston (Bromobutyle) et dun capuchon de protection</t>
+    <t>EFLUELDA TETRA, suspension injectable en seringue préremplie Vaccin grippal quadrivalent (inactivé, à virion fragmenté), 60 microgrammes HA/souche 1 seringue préremplie en verre de 0,7 ml avec aiguille séparée, munie d'un bouchon-piston (Bromobutyle) et d'un capuchon de protection</t>
   </si>
   <si>
     <t>VAC0079</t>
@@ -954,7 +951,7 @@
     <t>3400930071595</t>
   </si>
   <si>
-    <t>RABIPUR, poudre et solvant pour solution injectable en seringue préremplie. Vaccin rabique (inactivé) 1 flacon en verre - 1 seringue préremplie en verre de 1 ml et 2 aiguilles séparées une pour la reconstitution et une pour ladministration</t>
+    <t>RABIPUR, poudre et solvant pour solution injectable en seringue préremplie. Vaccin rabique (inactivé) 1 flacon en verre - 1 seringue préremplie en verre de 1 ml et 2 aiguilles séparées une pour la reconstitution et une pour l'administration</t>
   </si>
   <si>
     <t>VAC0060</t>
@@ -1248,13 +1245,13 @@
     <t>3400935524737</t>
   </si>
   <si>
-    <t>INFANRIXQUINTA, poudre et suspension pour suspension injectable. Vaccin diphtérique (D), tétanique (T), coquelucheux (acellulaire, multicomposé) (Ca), poliomyélitique (inactivé) (P) et conjugué de lHaemophilus influenzae type b (Hib), adsorbé 1 flacon(s) en verre - 1 seringue(s) préremplie(s) en verre de 0,5 ml avec aiguille(s) séparée(s)</t>
+    <t>INFANRIXQUINTA, poudre et suspension pour suspension injectable. Vaccin diphtérique (D), tétanique (T), coquelucheux (acellulaire, multicomposé) (Ca), poliomyélitique (inactivé) (P) et conjugué de l'Haemophilus influenzae type b (Hib), adsorbé 1 flacon(s) en verre - 1 seringue(s) préremplie(s) en verre de 0,5 ml avec aiguille(s) séparée(s)</t>
   </si>
   <si>
     <t>69543678</t>
   </si>
   <si>
-    <t>INFANRIXQUINTA, poudre et suspension pour suspension injectable. Vaccin diphtérique (D), tétanique (T), coquelucheux (acellulaire, multicomposé) (Ca), poliomyélitique (inactivé) (P) et conjugué de lHaemophilus influenzae type b (Hib), adsorbé</t>
+    <t>INFANRIXQUINTA, poudre et suspension pour suspension injectable. Vaccin diphtérique (D), tétanique (T), coquelucheux (acellulaire, multicomposé) (Ca), poliomyélitique (inactivé) (P) et conjugué de l'Haemophilus influenzae type b (Hib), adsorbé</t>
   </si>
   <si>
     <t>VAC0567</t>
@@ -2069,24 +2066,22 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" t="s" s="2">
-        <v>25</v>
-      </c>
+      <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>26</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>28</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -2101,3334 +2096,3334 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>30</v>
       </c>
-      <c r="C1" t="s" s="1">
-        <v>31</v>
-      </c>
       <c r="D1" t="s" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>32</v>
       </c>
-      <c r="B2" t="s" s="2">
+      <c r="C2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D2" t="s" s="2">
         <v>33</v>
       </c>
-      <c r="C2" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>34</v>
-      </c>
       <c r="E2" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="B3" t="s" s="2">
-        <v>36</v>
-      </c>
       <c r="C3" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="D3" t="s" s="2">
+      <c r="E3" t="s" s="2">
         <v>38</v>
-      </c>
-      <c r="E3" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="B4" t="s" s="2">
-        <v>36</v>
-      </c>
       <c r="C4" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E4" t="s" s="2">
         <v>40</v>
-      </c>
-      <c r="E4" t="s" s="2">
-        <v>41</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>42</v>
       </c>
-      <c r="B5" t="s" s="2">
+      <c r="C5" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D5" t="s" s="2">
         <v>43</v>
       </c>
-      <c r="C5" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D5" t="s" s="2">
+      <c r="E5" t="s" s="2">
         <v>44</v>
-      </c>
-      <c r="E5" t="s" s="2">
-        <v>45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>42</v>
       </c>
-      <c r="B6" t="s" s="2">
-        <v>43</v>
-      </c>
       <c r="C6" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="E6" t="s" s="2">
         <v>46</v>
-      </c>
-      <c r="E6" t="s" s="2">
-        <v>47</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="B7" t="s" s="2">
+      <c r="C7" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s" s="2">
         <v>49</v>
       </c>
-      <c r="C7" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D7" t="s" s="2">
+      <c r="E7" t="s" s="2">
         <v>50</v>
-      </c>
-      <c r="E7" t="s" s="2">
-        <v>51</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="B8" t="s" s="2">
-        <v>49</v>
-      </c>
       <c r="C8" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="E8" t="s" s="2">
         <v>52</v>
-      </c>
-      <c r="E8" t="s" s="2">
-        <v>53</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="B9" t="s" s="2">
+      <c r="C9" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="C9" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D9" t="s" s="2">
+      <c r="E9" t="s" s="2">
         <v>56</v>
-      </c>
-      <c r="E9" t="s" s="2">
-        <v>57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="B10" t="s" s="2">
-        <v>55</v>
-      </c>
       <c r="C10" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="E10" t="s" s="2">
         <v>58</v>
-      </c>
-      <c r="E10" t="s" s="2">
-        <v>59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="B11" t="s" s="2">
+      <c r="C11" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s" s="2">
         <v>61</v>
       </c>
-      <c r="C11" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D11" t="s" s="2">
+      <c r="E11" t="s" s="2">
         <v>62</v>
-      </c>
-      <c r="E11" t="s" s="2">
-        <v>63</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="B12" t="s" s="2">
-        <v>61</v>
-      </c>
       <c r="C12" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E12" t="s" s="2">
         <v>64</v>
-      </c>
-      <c r="E12" t="s" s="2">
-        <v>65</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="B13" t="s" s="2">
-        <v>61</v>
-      </c>
       <c r="C13" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="E13" t="s" s="2">
         <v>66</v>
-      </c>
-      <c r="E13" t="s" s="2">
-        <v>67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>68</v>
       </c>
-      <c r="B14" t="s" s="2">
+      <c r="C14" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D14" t="s" s="2">
         <v>69</v>
       </c>
-      <c r="C14" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D14" t="s" s="2">
+      <c r="E14" t="s" s="2">
         <v>70</v>
-      </c>
-      <c r="E14" t="s" s="2">
-        <v>71</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>68</v>
       </c>
-      <c r="B15" t="s" s="2">
-        <v>69</v>
-      </c>
       <c r="C15" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E15" t="s" s="2">
         <v>72</v>
-      </c>
-      <c r="E15" t="s" s="2">
-        <v>73</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="B16" t="s" s="2">
+      <c r="C16" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D16" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="C16" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D16" t="s" s="2">
+      <c r="E16" t="s" s="2">
         <v>76</v>
-      </c>
-      <c r="E16" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="B17" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="C17" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E17" t="s" s="2">
         <v>78</v>
-      </c>
-      <c r="E17" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="B18" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="C18" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E18" t="s" s="2">
         <v>80</v>
-      </c>
-      <c r="E18" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="B19" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="C19" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E19" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="E19" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="B20" t="s" s="2">
+      <c r="C20" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D20" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="C20" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D20" t="s" s="2">
+      <c r="E20" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="E20" t="s" s="2">
-        <v>87</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="B21" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="C21" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="E21" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="E21" t="s" s="2">
-        <v>89</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="B22" t="s" s="2">
+      <c r="C22" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D22" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="C22" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D22" t="s" s="2">
+      <c r="E22" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="E22" t="s" s="2">
-        <v>93</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="B23" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="C23" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D23" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="E23" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="E23" t="s" s="2">
-        <v>95</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="B24" t="s" s="2">
+      <c r="C24" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D24" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="C24" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D24" t="s" s="2">
+      <c r="E24" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="E24" t="s" s="2">
-        <v>99</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="B25" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="C25" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="E25" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="E25" t="s" s="2">
-        <v>101</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="B26" t="s" s="2">
+      <c r="C26" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D26" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="C26" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D26" t="s" s="2">
+      <c r="E26" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="E26" t="s" s="2">
-        <v>105</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="B27" t="s" s="2">
-        <v>103</v>
-      </c>
       <c r="C27" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D27" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="E27" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="E27" t="s" s="2">
-        <v>107</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="B28" t="s" s="2">
+      <c r="C28" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D28" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="C28" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D28" t="s" s="2">
+      <c r="E28" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="E28" t="s" s="2">
-        <v>111</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="B29" t="s" s="2">
-        <v>109</v>
-      </c>
       <c r="C29" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D29" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E29" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="E29" t="s" s="2">
-        <v>113</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="B30" t="s" s="2">
+      <c r="C30" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D30" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="C30" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D30" t="s" s="2">
+      <c r="E30" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="E30" t="s" s="2">
-        <v>117</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="B31" t="s" s="2">
-        <v>115</v>
-      </c>
       <c r="C31" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D31" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="E31" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="E31" t="s" s="2">
-        <v>119</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="B32" t="s" s="2">
+      <c r="C32" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D32" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="C32" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D32" t="s" s="2">
+      <c r="E32" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="E32" t="s" s="2">
-        <v>123</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="B33" t="s" s="2">
-        <v>121</v>
-      </c>
       <c r="C33" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D33" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="E33" t="s" s="2">
         <v>124</v>
-      </c>
-      <c r="E33" t="s" s="2">
-        <v>125</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="B34" t="s" s="2">
+      <c r="C34" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D34" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="C34" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D34" t="s" s="2">
+      <c r="E34" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="E34" t="s" s="2">
-        <v>129</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="B35" t="s" s="2">
+      <c r="C35" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D35" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="C35" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D35" t="s" s="2">
+      <c r="E35" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="E35" t="s" s="2">
-        <v>133</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B36" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="B36" t="s" s="2">
-        <v>131</v>
-      </c>
       <c r="C36" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D36" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E36" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="E36" t="s" s="2">
-        <v>135</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="B37" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="B37" t="s" s="2">
+      <c r="C37" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D37" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="C37" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D37" t="s" s="2">
+      <c r="E37" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="E37" t="s" s="2">
-        <v>139</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="B38" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="B38" t="s" s="2">
-        <v>137</v>
-      </c>
       <c r="C38" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D38" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="E38" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="E38" t="s" s="2">
-        <v>141</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B39" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="B39" t="s" s="2">
+      <c r="C39" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D39" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="C39" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D39" t="s" s="2">
+      <c r="E39" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="E39" t="s" s="2">
-        <v>145</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B40" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="B40" t="s" s="2">
-        <v>143</v>
-      </c>
       <c r="C40" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D40" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="E40" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="E40" t="s" s="2">
-        <v>147</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="B41" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="B41" t="s" s="2">
+      <c r="C41" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D41" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="C41" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D41" t="s" s="2">
+      <c r="E41" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="E41" t="s" s="2">
-        <v>151</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="B42" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="B42" t="s" s="2">
-        <v>149</v>
-      </c>
       <c r="C42" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D42" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="E42" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="E42" t="s" s="2">
-        <v>153</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="B43" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="B43" t="s" s="2">
+      <c r="C43" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D43" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="C43" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D43" t="s" s="2">
+      <c r="E43" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="E43" t="s" s="2">
-        <v>157</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="B44" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="B44" t="s" s="2">
-        <v>155</v>
-      </c>
       <c r="C44" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D44" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="E44" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="E44" t="s" s="2">
-        <v>159</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="B45" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="B45" t="s" s="2">
+      <c r="C45" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D45" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="C45" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D45" t="s" s="2">
+      <c r="E45" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="E45" t="s" s="2">
-        <v>163</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="B46" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="B46" t="s" s="2">
-        <v>161</v>
-      </c>
       <c r="C46" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D46" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="E46" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="E46" t="s" s="2">
-        <v>165</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="B47" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="B47" t="s" s="2">
-        <v>161</v>
-      </c>
       <c r="C47" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D47" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="E47" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="E47" t="s" s="2">
-        <v>167</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="B48" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="B48" t="s" s="2">
-        <v>161</v>
-      </c>
       <c r="C48" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D48" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="E48" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="E48" t="s" s="2">
-        <v>169</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="B49" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="B49" t="s" s="2">
-        <v>161</v>
-      </c>
       <c r="C49" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D49" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="E49" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="E49" t="s" s="2">
-        <v>171</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="B50" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="B50" t="s" s="2">
+      <c r="C50" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D50" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="C50" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D50" t="s" s="2">
+      <c r="E50" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="E50" t="s" s="2">
-        <v>175</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="B51" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="B51" t="s" s="2">
-        <v>173</v>
-      </c>
       <c r="C51" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D51" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="E51" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="E51" t="s" s="2">
-        <v>177</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="B52" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="B52" t="s" s="2">
+      <c r="C52" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D52" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="C52" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D52" t="s" s="2">
+      <c r="E52" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="E52" t="s" s="2">
-        <v>181</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="B53" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="B53" t="s" s="2">
-        <v>179</v>
-      </c>
       <c r="C53" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D53" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="E53" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="E53" t="s" s="2">
-        <v>183</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="B54" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="B54" t="s" s="2">
+      <c r="C54" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D54" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="C54" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D54" t="s" s="2">
+      <c r="E54" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="E54" t="s" s="2">
-        <v>187</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="B55" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="B55" t="s" s="2">
-        <v>185</v>
-      </c>
       <c r="C55" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D55" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="E55" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="E55" t="s" s="2">
-        <v>189</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="B56" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="B56" t="s" s="2">
+      <c r="C56" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D56" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="C56" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D56" t="s" s="2">
+      <c r="E56" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="E56" t="s" s="2">
-        <v>193</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="B57" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="B57" t="s" s="2">
-        <v>191</v>
-      </c>
       <c r="C57" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D57" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="E57" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="E57" t="s" s="2">
-        <v>195</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="B58" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="B58" t="s" s="2">
+      <c r="C58" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D58" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="C58" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D58" t="s" s="2">
+      <c r="E58" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="E58" t="s" s="2">
-        <v>199</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="B59" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="B59" t="s" s="2">
+      <c r="C59" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D59" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="C59" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D59" t="s" s="2">
+      <c r="E59" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="E59" t="s" s="2">
-        <v>203</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="B60" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="B60" t="s" s="2">
-        <v>201</v>
-      </c>
       <c r="C60" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D60" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="E60" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="E60" t="s" s="2">
-        <v>205</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="B61" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="B61" t="s" s="2">
+      <c r="C61" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D61" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="C61" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D61" t="s" s="2">
+      <c r="E61" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="E61" t="s" s="2">
-        <v>209</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="B62" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="B62" t="s" s="2">
-        <v>207</v>
-      </c>
       <c r="C62" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D62" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="E62" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="E62" t="s" s="2">
-        <v>211</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="B63" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="B63" t="s" s="2">
+      <c r="C63" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D63" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="C63" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D63" t="s" s="2">
+      <c r="E63" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="E63" t="s" s="2">
-        <v>215</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="B64" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="B64" t="s" s="2">
-        <v>213</v>
-      </c>
       <c r="C64" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D64" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="E64" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="E64" t="s" s="2">
-        <v>217</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="B65" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="B65" t="s" s="2">
+      <c r="C65" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D65" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="C65" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D65" t="s" s="2">
+      <c r="E65" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="E65" t="s" s="2">
-        <v>221</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="B66" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="B66" t="s" s="2">
-        <v>219</v>
-      </c>
       <c r="C66" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D66" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="E66" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="E66" t="s" s="2">
-        <v>223</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="B67" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="B67" t="s" s="2">
+      <c r="C67" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D67" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="C67" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D67" t="s" s="2">
+      <c r="E67" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="E67" t="s" s="2">
-        <v>227</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="B68" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="B68" t="s" s="2">
+      <c r="C68" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D68" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="C68" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D68" t="s" s="2">
+      <c r="E68" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="E68" t="s" s="2">
-        <v>231</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="B69" t="s" s="2">
-        <v>229</v>
-      </c>
       <c r="C69" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D69" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="E69" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="E69" t="s" s="2">
-        <v>233</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="B70" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="B70" t="s" s="2">
-        <v>229</v>
-      </c>
       <c r="C70" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D70" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="E70" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="E70" t="s" s="2">
-        <v>235</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="B71" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="B71" t="s" s="2">
-        <v>229</v>
-      </c>
       <c r="C71" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D71" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="E71" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="E71" t="s" s="2">
-        <v>237</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="B72" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="B72" t="s" s="2">
+      <c r="C72" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D72" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="C72" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D72" t="s" s="2">
+      <c r="E72" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="E72" t="s" s="2">
-        <v>241</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="B73" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="B73" t="s" s="2">
-        <v>239</v>
-      </c>
       <c r="C73" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D73" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="E73" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="E73" t="s" s="2">
-        <v>243</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="B74" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="B74" t="s" s="2">
+      <c r="C74" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D74" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="C74" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D74" t="s" s="2">
+      <c r="E74" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="E74" t="s" s="2">
-        <v>247</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="B75" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="B75" t="s" s="2">
-        <v>245</v>
-      </c>
       <c r="C75" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D75" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="E75" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="E75" t="s" s="2">
-        <v>249</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="B76" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="B76" t="s" s="2">
+      <c r="C76" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D76" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="C76" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D76" t="s" s="2">
+      <c r="E76" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="E76" t="s" s="2">
-        <v>253</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="B77" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="B77" t="s" s="2">
-        <v>251</v>
-      </c>
       <c r="C77" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D77" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="E77" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="E77" t="s" s="2">
-        <v>255</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="B78" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="B78" t="s" s="2">
-        <v>251</v>
-      </c>
       <c r="C78" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D78" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="E78" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="E78" t="s" s="2">
-        <v>257</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="B79" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="B79" t="s" s="2">
+      <c r="C79" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D79" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="C79" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D79" t="s" s="2">
+      <c r="E79" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="E79" t="s" s="2">
-        <v>261</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="B80" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="B80" t="s" s="2">
-        <v>259</v>
-      </c>
       <c r="C80" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D80" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="E80" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="E80" t="s" s="2">
-        <v>263</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="B81" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="B81" t="s" s="2">
-        <v>259</v>
-      </c>
       <c r="C81" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D81" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="E81" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="E81" t="s" s="2">
-        <v>265</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="B82" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="B82" t="s" s="2">
-        <v>259</v>
-      </c>
       <c r="C82" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D82" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="E82" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="E82" t="s" s="2">
-        <v>267</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="B83" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="B83" t="s" s="2">
+      <c r="C83" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D83" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="C83" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D83" t="s" s="2">
+      <c r="E83" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="E83" t="s" s="2">
-        <v>271</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B84" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="B84" t="s" s="2">
+      <c r="C84" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D84" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="C84" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D84" t="s" s="2">
+      <c r="E84" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="E84" t="s" s="2">
-        <v>275</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B85" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="B85" t="s" s="2">
-        <v>273</v>
-      </c>
       <c r="C85" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D85" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="E85" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="E85" t="s" s="2">
-        <v>277</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="B86" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="B86" t="s" s="2">
+      <c r="C86" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D86" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="C86" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D86" t="s" s="2">
+      <c r="E86" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="E86" t="s" s="2">
-        <v>281</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="B87" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="B87" t="s" s="2">
-        <v>279</v>
-      </c>
       <c r="C87" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D87" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="E87" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="E87" t="s" s="2">
-        <v>283</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="B88" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="B88" t="s" s="2">
+      <c r="C88" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D88" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="C88" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D88" t="s" s="2">
+      <c r="E88" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="E88" t="s" s="2">
-        <v>287</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="B89" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="B89" t="s" s="2">
-        <v>285</v>
-      </c>
       <c r="C89" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D89" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="E89" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="E89" t="s" s="2">
-        <v>289</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="B90" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="B90" t="s" s="2">
+      <c r="C90" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D90" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="C90" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D90" t="s" s="2">
+      <c r="E90" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="E90" t="s" s="2">
-        <v>293</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="B91" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="B91" t="s" s="2">
-        <v>291</v>
-      </c>
       <c r="C91" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D91" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="E91" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="E91" t="s" s="2">
-        <v>295</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="B92" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="B92" t="s" s="2">
+      <c r="C92" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D92" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="C92" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D92" t="s" s="2">
+      <c r="E92" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="E92" t="s" s="2">
-        <v>299</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="B93" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="B93" t="s" s="2">
+      <c r="C93" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D93" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="C93" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D93" t="s" s="2">
+      <c r="E93" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="E93" t="s" s="2">
-        <v>303</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="B94" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="B94" t="s" s="2">
-        <v>301</v>
-      </c>
       <c r="C94" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D94" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="E94" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="E94" t="s" s="2">
-        <v>305</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="B95" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="B95" t="s" s="2">
-        <v>301</v>
-      </c>
       <c r="C95" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D95" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="E95" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="E95" t="s" s="2">
-        <v>307</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="B96" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="B96" t="s" s="2">
+      <c r="C96" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D96" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="C96" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D96" t="s" s="2">
+      <c r="E96" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="E96" t="s" s="2">
-        <v>311</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="B97" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="B97" t="s" s="2">
-        <v>309</v>
-      </c>
       <c r="C97" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D97" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="E97" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="E97" t="s" s="2">
-        <v>313</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="B98" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="B98" t="s" s="2">
+      <c r="C98" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D98" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="C98" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D98" t="s" s="2">
+      <c r="E98" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="E98" t="s" s="2">
-        <v>317</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="B99" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="B99" t="s" s="2">
-        <v>315</v>
-      </c>
       <c r="C99" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D99" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="E99" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="E99" t="s" s="2">
-        <v>319</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="B100" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="B100" t="s" s="2">
+      <c r="C100" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D100" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="C100" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D100" t="s" s="2">
+      <c r="E100" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="E100" t="s" s="2">
-        <v>323</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="B101" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="B101" t="s" s="2">
-        <v>321</v>
-      </c>
       <c r="C101" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D101" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="E101" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="E101" t="s" s="2">
-        <v>325</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="B102" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="B102" t="s" s="2">
+      <c r="C102" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D102" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="C102" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D102" t="s" s="2">
+      <c r="E102" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="E102" t="s" s="2">
-        <v>329</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="B103" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="B103" t="s" s="2">
-        <v>327</v>
-      </c>
       <c r="C103" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D103" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="E103" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="E103" t="s" s="2">
-        <v>331</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="B104" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="B104" t="s" s="2">
+      <c r="C104" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D104" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="C104" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D104" t="s" s="2">
+      <c r="E104" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="E104" t="s" s="2">
-        <v>335</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="B105" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="B105" t="s" s="2">
-        <v>333</v>
-      </c>
       <c r="C105" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D105" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="E105" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="E105" t="s" s="2">
-        <v>337</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B106" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="B106" t="s" s="2">
+      <c r="C106" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D106" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="C106" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D106" t="s" s="2">
+      <c r="E106" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="E106" t="s" s="2">
-        <v>341</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B107" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="B107" t="s" s="2">
-        <v>339</v>
-      </c>
       <c r="C107" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D107" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="E107" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="E107" t="s" s="2">
-        <v>343</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="B108" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="B108" t="s" s="2">
+      <c r="C108" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D108" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="C108" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D108" t="s" s="2">
+      <c r="E108" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="E108" t="s" s="2">
-        <v>347</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="B109" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="B109" t="s" s="2">
-        <v>345</v>
-      </c>
       <c r="C109" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D109" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="E109" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="E109" t="s" s="2">
-        <v>349</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="B110" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="B110" t="s" s="2">
+      <c r="C110" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D110" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="C110" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D110" t="s" s="2">
+      <c r="E110" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="E110" t="s" s="2">
-        <v>353</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="B111" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="B111" t="s" s="2">
-        <v>351</v>
-      </c>
       <c r="C111" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D111" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="E111" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="E111" t="s" s="2">
-        <v>355</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B112" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="B112" t="s" s="2">
+      <c r="C112" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D112" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="C112" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D112" t="s" s="2">
+      <c r="E112" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="E112" t="s" s="2">
-        <v>359</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B113" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="B113" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="C113" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D113" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="E113" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="E113" t="s" s="2">
-        <v>361</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B114" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="B114" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="C114" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D114" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="E114" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="E114" t="s" s="2">
-        <v>363</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="B115" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="B115" t="s" s="2">
+      <c r="C115" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D115" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="C115" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D115" t="s" s="2">
+      <c r="E115" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="E115" t="s" s="2">
-        <v>367</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="B116" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="B116" t="s" s="2">
-        <v>365</v>
-      </c>
       <c r="C116" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D116" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="E116" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="E116" t="s" s="2">
-        <v>369</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B117" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="B117" t="s" s="2">
+      <c r="C117" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D117" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="C117" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D117" t="s" s="2">
+      <c r="E117" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="E117" t="s" s="2">
-        <v>373</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B118" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="B118" t="s" s="2">
-        <v>371</v>
-      </c>
       <c r="C118" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D118" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="E118" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="E118" t="s" s="2">
-        <v>375</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B119" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="B119" t="s" s="2">
-        <v>371</v>
-      </c>
       <c r="C119" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D119" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="E119" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="E119" t="s" s="2">
-        <v>377</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B120" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="B120" t="s" s="2">
+      <c r="C120" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D120" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="C120" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D120" t="s" s="2">
+      <c r="E120" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="E120" t="s" s="2">
-        <v>381</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B121" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="B121" t="s" s="2">
-        <v>379</v>
-      </c>
       <c r="C121" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D121" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="E121" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="E121" t="s" s="2">
-        <v>383</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="B122" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="B122" t="s" s="2">
+      <c r="C122" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D122" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="C122" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D122" t="s" s="2">
+      <c r="E122" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="E122" t="s" s="2">
-        <v>387</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="B123" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="B123" t="s" s="2">
-        <v>385</v>
-      </c>
       <c r="C123" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D123" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="E123" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="E123" t="s" s="2">
-        <v>389</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="B124" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="B124" t="s" s="2">
+      <c r="C124" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D124" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="C124" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D124" t="s" s="2">
+      <c r="E124" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="E124" t="s" s="2">
-        <v>393</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="B125" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="B125" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="C125" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D125" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="E125" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="E125" t="s" s="2">
-        <v>395</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B126" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="B126" t="s" s="2">
+      <c r="C126" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D126" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="C126" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D126" t="s" s="2">
+      <c r="E126" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="E126" t="s" s="2">
-        <v>399</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B127" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="B127" t="s" s="2">
-        <v>397</v>
-      </c>
       <c r="C127" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D127" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="E127" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="E127" t="s" s="2">
-        <v>401</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B128" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="B128" t="s" s="2">
+      <c r="C128" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D128" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="C128" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D128" t="s" s="2">
+      <c r="E128" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="E128" t="s" s="2">
-        <v>405</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B129" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="B129" t="s" s="2">
-        <v>403</v>
-      </c>
       <c r="C129" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D129" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="E129" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="E129" t="s" s="2">
-        <v>407</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B130" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="B130" t="s" s="2">
+      <c r="C130" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D130" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="C130" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D130" t="s" s="2">
+      <c r="E130" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="E130" t="s" s="2">
-        <v>411</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B131" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="B131" t="s" s="2">
-        <v>409</v>
-      </c>
       <c r="C131" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D131" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="E131" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="E131" t="s" s="2">
-        <v>413</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B132" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="B132" t="s" s="2">
+      <c r="C132" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D132" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="C132" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D132" t="s" s="2">
+      <c r="E132" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="E132" t="s" s="2">
-        <v>417</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B133" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="B133" t="s" s="2">
-        <v>415</v>
-      </c>
       <c r="C133" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D133" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="E133" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="E133" t="s" s="2">
-        <v>419</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B134" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="B134" t="s" s="2">
+      <c r="C134" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D134" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="C134" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D134" t="s" s="2">
+      <c r="E134" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="E134" t="s" s="2">
-        <v>423</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B135" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="B135" t="s" s="2">
-        <v>421</v>
-      </c>
       <c r="C135" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D135" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="E135" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="E135" t="s" s="2">
-        <v>425</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="B136" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="B136" t="s" s="2">
+      <c r="C136" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D136" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="C136" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D136" t="s" s="2">
+      <c r="E136" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="E136" t="s" s="2">
-        <v>429</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="B137" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="B137" t="s" s="2">
-        <v>427</v>
-      </c>
       <c r="C137" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D137" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="E137" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="E137" t="s" s="2">
-        <v>431</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="B138" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="B138" t="s" s="2">
+      <c r="C138" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D138" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="C138" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D138" t="s" s="2">
+      <c r="E138" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="E138" t="s" s="2">
-        <v>435</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="B139" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="B139" t="s" s="2">
-        <v>433</v>
-      </c>
       <c r="C139" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D139" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="E139" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="E139" t="s" s="2">
-        <v>437</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B140" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="B140" t="s" s="2">
+      <c r="C140" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D140" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="C140" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D140" t="s" s="2">
+      <c r="E140" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="E140" t="s" s="2">
-        <v>441</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B141" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="B141" t="s" s="2">
-        <v>439</v>
-      </c>
       <c r="C141" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D141" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="E141" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="E141" t="s" s="2">
-        <v>443</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B142" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="B142" t="s" s="2">
+      <c r="C142" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D142" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="C142" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D142" t="s" s="2">
+      <c r="E142" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="E142" t="s" s="2">
-        <v>447</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B143" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="B143" t="s" s="2">
-        <v>445</v>
-      </c>
       <c r="C143" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D143" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="E143" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="E143" t="s" s="2">
-        <v>449</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B144" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="B144" t="s" s="2">
+      <c r="C144" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D144" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="C144" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D144" t="s" s="2">
+      <c r="E144" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="E144" t="s" s="2">
-        <v>453</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B145" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="B145" t="s" s="2">
-        <v>451</v>
-      </c>
       <c r="C145" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D145" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="E145" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="E145" t="s" s="2">
-        <v>455</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B146" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="B146" t="s" s="2">
+      <c r="C146" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D146" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="C146" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D146" t="s" s="2">
+      <c r="E146" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="E146" t="s" s="2">
-        <v>459</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B147" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="B147" t="s" s="2">
-        <v>457</v>
-      </c>
       <c r="C147" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D147" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="E147" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="E147" t="s" s="2">
-        <v>461</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="B148" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="B148" t="s" s="2">
+      <c r="C148" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D148" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="C148" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D148" t="s" s="2">
+      <c r="E148" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="E148" t="s" s="2">
-        <v>465</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="B149" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="B149" t="s" s="2">
-        <v>463</v>
-      </c>
       <c r="C149" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D149" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="E149" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="E149" t="s" s="2">
-        <v>467</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="B150" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="B150" t="s" s="2">
+      <c r="C150" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D150" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="C150" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D150" t="s" s="2">
+      <c r="E150" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="E150" t="s" s="2">
-        <v>471</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="B151" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="B151" t="s" s="2">
-        <v>469</v>
-      </c>
       <c r="C151" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D151" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="E151" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="E151" t="s" s="2">
-        <v>473</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="B152" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="B152" t="s" s="2">
+      <c r="C152" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D152" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="C152" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D152" t="s" s="2">
+      <c r="E152" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="E152" t="s" s="2">
-        <v>477</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="B153" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="B153" t="s" s="2">
-        <v>475</v>
-      </c>
       <c r="C153" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D153" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="E153" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="E153" t="s" s="2">
-        <v>479</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B154" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="B154" t="s" s="2">
+      <c r="C154" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D154" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="C154" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D154" t="s" s="2">
+      <c r="E154" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="E154" t="s" s="2">
-        <v>483</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B155" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="B155" t="s" s="2">
-        <v>481</v>
-      </c>
       <c r="C155" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D155" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="E155" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="E155" t="s" s="2">
-        <v>485</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="B156" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="B156" t="s" s="2">
+      <c r="C156" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D156" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="C156" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D156" t="s" s="2">
+      <c r="E156" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="E156" t="s" s="2">
-        <v>489</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="B157" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="B157" t="s" s="2">
-        <v>487</v>
-      </c>
       <c r="C157" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D157" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="E157" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="E157" t="s" s="2">
-        <v>491</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="B158" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="B158" t="s" s="2">
+      <c r="C158" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D158" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="C158" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D158" t="s" s="2">
+      <c r="E158" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="E158" t="s" s="2">
-        <v>495</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="B159" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="B159" t="s" s="2">
-        <v>493</v>
-      </c>
       <c r="C159" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D159" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="E159" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="E159" t="s" s="2">
-        <v>497</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="B160" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="B160" t="s" s="2">
-        <v>493</v>
-      </c>
       <c r="C160" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D160" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="E160" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="E160" t="s" s="2">
-        <v>499</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B161" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="B161" t="s" s="2">
+      <c r="C161" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D161" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="C161" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D161" t="s" s="2">
+      <c r="E161" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="E161" t="s" s="2">
-        <v>503</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B162" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="B162" t="s" s="2">
-        <v>501</v>
-      </c>
       <c r="C162" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D162" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="E162" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="E162" t="s" s="2">
-        <v>505</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="B163" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="B163" t="s" s="2">
+      <c r="C163" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D163" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="C163" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D163" t="s" s="2">
+      <c r="E163" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="E163" t="s" s="2">
-        <v>509</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="B164" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="B164" t="s" s="2">
-        <v>507</v>
-      </c>
       <c r="C164" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D164" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="E164" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="E164" t="s" s="2">
-        <v>511</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="B165" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="B165" t="s" s="2">
+      <c r="C165" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D165" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="C165" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D165" t="s" s="2">
+      <c r="E165" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="E165" t="s" s="2">
-        <v>515</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="B166" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="B166" t="s" s="2">
-        <v>513</v>
-      </c>
       <c r="C166" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D166" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="E166" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="E166" t="s" s="2">
-        <v>517</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="B167" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="B167" t="s" s="2">
+      <c r="C167" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D167" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="C167" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D167" t="s" s="2">
+      <c r="E167" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="E167" t="s" s="2">
-        <v>521</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="B168" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="B168" t="s" s="2">
-        <v>519</v>
-      </c>
       <c r="C168" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D168" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="E168" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="E168" t="s" s="2">
-        <v>523</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B169" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="B169" t="s" s="2">
+      <c r="C169" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D169" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="C169" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D169" t="s" s="2">
+      <c r="E169" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="E169" t="s" s="2">
-        <v>527</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B170" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="B170" t="s" s="2">
-        <v>525</v>
-      </c>
       <c r="C170" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D170" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="E170" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="E170" t="s" s="2">
-        <v>529</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="B171" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="B171" t="s" s="2">
+      <c r="C171" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D171" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="C171" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D171" t="s" s="2">
+      <c r="E171" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="E171" t="s" s="2">
-        <v>533</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="B172" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="B172" t="s" s="2">
-        <v>531</v>
-      </c>
       <c r="C172" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D172" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="E172" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="E172" t="s" s="2">
-        <v>535</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B173" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="B173" t="s" s="2">
+      <c r="C173" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D173" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="C173" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D173" t="s" s="2">
+      <c r="E173" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="E173" t="s" s="2">
-        <v>539</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B174" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="B174" t="s" s="2">
-        <v>537</v>
-      </c>
       <c r="C174" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D174" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="E174" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="E174" t="s" s="2">
-        <v>541</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B175" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="B175" t="s" s="2">
+      <c r="C175" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D175" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="C175" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D175" t="s" s="2">
+      <c r="E175" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="E175" t="s" s="2">
-        <v>545</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B176" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="B176" t="s" s="2">
+      <c r="C176" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D176" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="C176" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D176" t="s" s="2">
+      <c r="E176" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="E176" t="s" s="2">
-        <v>549</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B177" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="B177" t="s" s="2">
-        <v>547</v>
-      </c>
       <c r="C177" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D177" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="E177" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="E177" t="s" s="2">
-        <v>551</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="B178" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="B178" t="s" s="2">
+      <c r="C178" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D178" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="C178" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D178" t="s" s="2">
+      <c r="E178" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="E178" t="s" s="2">
-        <v>555</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="B179" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="B179" t="s" s="2">
-        <v>553</v>
-      </c>
       <c r="C179" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D179" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="E179" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="E179" t="s" s="2">
-        <v>557</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="B180" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="B180" t="s" s="2">
+      <c r="C180" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D180" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="C180" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D180" t="s" s="2">
+      <c r="E180" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="E180" t="s" s="2">
-        <v>561</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="B181" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="B181" t="s" s="2">
-        <v>559</v>
-      </c>
       <c r="C181" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D181" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="E181" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="E181" t="s" s="2">
-        <v>563</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="B182" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="B182" t="s" s="2">
+      <c r="C182" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D182" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="C182" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D182" t="s" s="2">
+      <c r="E182" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="E182" t="s" s="2">
-        <v>567</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="B183" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="B183" t="s" s="2">
-        <v>565</v>
-      </c>
       <c r="C183" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D183" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="E183" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="E183" t="s" s="2">
-        <v>569</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="B184" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="B184" t="s" s="2">
+      <c r="C184" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D184" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="C184" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D184" t="s" s="2">
+      <c r="E184" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="E184" t="s" s="2">
-        <v>573</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="B185" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="B185" t="s" s="2">
-        <v>571</v>
-      </c>
       <c r="C185" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D185" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="E185" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="E185" t="s" s="2">
-        <v>575</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="B186" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="B186" t="s" s="2">
+      <c r="C186" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D186" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="C186" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D186" t="s" s="2">
+      <c r="E186" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="E186" t="s" s="2">
-        <v>579</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="B187" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="B187" t="s" s="2">
-        <v>577</v>
-      </c>
       <c r="C187" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D187" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="E187" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="E187" t="s" s="2">
-        <v>581</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="B188" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="B188" t="s" s="2">
-        <v>577</v>
-      </c>
       <c r="C188" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D188" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="E188" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="E188" t="s" s="2">
-        <v>583</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="B189" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="B189" t="s" s="2">
-        <v>577</v>
-      </c>
       <c r="C189" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D189" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="E189" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="E189" t="s" s="2">
-        <v>585</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="B190" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="B190" t="s" s="2">
-        <v>577</v>
-      </c>
       <c r="C190" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D190" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="E190" t="s" s="2">
         <v>586</v>
-      </c>
-      <c r="E190" t="s" s="2">
-        <v>587</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="B191" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="B191" t="s" s="2">
-        <v>577</v>
-      </c>
       <c r="C191" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D191" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="E191" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="E191" t="s" s="2">
-        <v>589</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="B192" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="B192" t="s" s="2">
+      <c r="C192" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D192" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="C192" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D192" t="s" s="2">
+      <c r="E192" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="E192" t="s" s="2">
-        <v>593</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="B193" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="B193" t="s" s="2">
-        <v>591</v>
-      </c>
       <c r="C193" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D193" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="E193" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="E193" t="s" s="2">
-        <v>595</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="B194" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="B194" t="s" s="2">
-        <v>591</v>
-      </c>
       <c r="C194" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D194" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="E194" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="E194" t="s" s="2">
-        <v>597</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="B195" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="B195" t="s" s="2">
+      <c r="C195" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D195" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="C195" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D195" t="s" s="2">
+      <c r="E195" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="E195" t="s" s="2">
-        <v>601</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="B196" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="B196" t="s" s="2">
-        <v>599</v>
-      </c>
       <c r="C196" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D196" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="E196" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="E196" t="s" s="2">
-        <v>603</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/alignement-nuva-bdpm.xlsx
+++ b/ig/main/alignement-nuva-bdpm.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.939</t>
+    <t>1.0.946</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-03</t>
+    <t>2025-08-04</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/alignement-nuva-bdpm.xlsx
+++ b/ig/main/alignement-nuva-bdpm.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.946</t>
+    <t>1.0.992</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-04</t>
+    <t>2025-09-08</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/alignement-nuva-bdpm.xlsx
+++ b/ig/main/alignement-nuva-bdpm.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.992</t>
+    <t>1.0.1009</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08</t>
+    <t>2025-10-02</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/alignement-nuva-bdpm.xlsx
+++ b/ig/main/alignement-nuva-bdpm.xlsx
@@ -35,13 +35,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Alignement_Codes_CIP_CIS_NUVA_BDPM</t>
+    <t>Alignement_Codes_NUVA_CIS_CIP_BDMP</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>Aligner les codes CIS et CIP de NUVA avec les codes CIS et CIP du BDPM</t>
+    <t>Alignement des codes NUVA avec les codes CIS et CIP de la BDPM</t>
   </si>
   <si>
     <t>Status</t>

--- a/ig/main/alignement-nuva-bdpm.xlsx
+++ b/ig/main/alignement-nuva-bdpm.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1009</t>
+    <t>1.0.1030</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02</t>
+    <t>2025-11-06</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/alignement-nuva-bdpm.xlsx
+++ b/ig/main/alignement-nuva-bdpm.xlsx
@@ -89,13 +89,13 @@
     <t>Source</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/terminologie-nuva?vs</t>
+    <t>https://smt.esante.gouv.fr/terminologie-nuva?vs|20241106120000</t>
   </si>
   <si>
     <t>Target</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/terminologie-bdpm?vs</t>
+    <t>https://smt.esante.gouv.fr/terminologie-bdpm?vs|20241106120000</t>
   </si>
 </sst>
 </file>

--- a/ig/main/alignement-nuva-bdpm.xlsx
+++ b/ig/main/alignement-nuva-bdpm.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1030</t>
+    <t>1.0.1042</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-06</t>
+    <t>2025-12-04</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/alignement-nuva-bdpm.xlsx
+++ b/ig/main/alignement-nuva-bdpm.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1042</t>
+    <t>1.0.1052</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-04</t>
+    <t>2026-01-07</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/alignement-nuva-bdpm.xlsx
+++ b/ig/main/alignement-nuva-bdpm.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1052</t>
+    <t>1.0.1063</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07</t>
+    <t>2026-02-03</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/alignement-nuva-bdpm.xlsx
+++ b/ig/main/alignement-nuva-bdpm.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1063</t>
+    <t>1.0.1072</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03</t>
+    <t>2026-03-04</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/alignement-nuva-bdpm.xlsx
+++ b/ig/main/alignement-nuva-bdpm.xlsx
@@ -89,13 +89,13 @@
     <t>Source</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/terminologie-nuva?vs|20241106120000</t>
+    <t>https://smt.esante.gouv.fr/terminologie-nuva?vs</t>
   </si>
   <si>
     <t>Target</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/terminologie-bdpm?vs|20241106120000</t>
+    <t>https://smt.esante.gouv.fr/terminologie-bdpm?vs</t>
   </si>
 </sst>
 </file>

--- a/ig/main/alignement-nuva-bdpm.xlsx
+++ b/ig/main/alignement-nuva-bdpm.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1072</t>
+    <t>1.0.1078</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04</t>
+    <t>2026-04-03</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/alignement-nuva-bdpm.xlsx
+++ b/ig/main/alignement-nuva-bdpm.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1078</t>
+    <t>1.0.1096</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03</t>
+    <t>2026-05-07</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/alignement-nuva-bdpm.xlsx
+++ b/ig/main/alignement-nuva-bdpm.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1096</t>
+    <t>1.0.1108</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07</t>
+    <t>2026-06-03</t>
   </si>
   <si>
     <t>Publisher</t>
